--- a/Stock_OneClick/history/scan_result_20260603_103229.xlsx
+++ b/Stock_OneClick/history/scan_result_20260603_103229.xlsx
@@ -509,7 +509,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q247"/>
+  <dimension ref="A1:Q246"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="19" customWidth="1" min="1" max="1"/>
@@ -670,24 +670,6 @@
       <c r="J3" t="n">
         <v>50.38</v>
       </c>
-      <c r="K3" t="n">
-        <v/>
-      </c>
-      <c r="L3" t="n">
-        <v/>
-      </c>
-      <c r="M3" t="n">
-        <v/>
-      </c>
-      <c r="N3" t="n">
-        <v/>
-      </c>
-      <c r="O3" t="n">
-        <v/>
-      </c>
-      <c r="P3" t="n">
-        <v/>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
           <t>D0=50.66; 最新=2026-06-03; 相对D0=-0.55%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复3次; 重复日期=2026-05-27, 2026-06-01, 2026-06-03</t>
@@ -739,24 +721,6 @@
       <c r="J4" t="n">
         <v>617.7</v>
       </c>
-      <c r="K4" t="n">
-        <v/>
-      </c>
-      <c r="L4" t="n">
-        <v/>
-      </c>
-      <c r="M4" t="n">
-        <v/>
-      </c>
-      <c r="N4" t="n">
-        <v/>
-      </c>
-      <c r="O4" t="n">
-        <v/>
-      </c>
-      <c r="P4" t="n">
-        <v/>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
           <t>D0=610.26; 最新=2026-06-03; 相对D0=1.22%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-26, 2026-06-03</t>
@@ -808,24 +772,6 @@
       <c r="J5" t="n">
         <v>23.435</v>
       </c>
-      <c r="K5" t="n">
-        <v/>
-      </c>
-      <c r="L5" t="n">
-        <v/>
-      </c>
-      <c r="M5" t="n">
-        <v/>
-      </c>
-      <c r="N5" t="n">
-        <v/>
-      </c>
-      <c r="O5" t="n">
-        <v/>
-      </c>
-      <c r="P5" t="n">
-        <v/>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-06-03; 相对D0=4.11%; 本次触发=2026-06-03(预警买入); 历史重复3次; 重复日期=2026-05-26, 2026-06-02, 2026-06-03</t>
@@ -877,24 +823,6 @@
       <c r="J6" t="n">
         <v>383.8</v>
       </c>
-      <c r="K6" t="n">
-        <v/>
-      </c>
-      <c r="L6" t="n">
-        <v/>
-      </c>
-      <c r="M6" t="n">
-        <v/>
-      </c>
-      <c r="N6" t="n">
-        <v/>
-      </c>
-      <c r="O6" t="n">
-        <v/>
-      </c>
-      <c r="P6" t="n">
-        <v/>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
           <t>D0=388.47; 最新=2026-06-03; 相对D0=-1.20%; 本次触发=2026-06-03(正式买入 | 预警买入); 历史重复2次; 重复日期=2026-05-27, 2026-06-03</t>
@@ -946,24 +874,12 @@
       <c r="J7" s="5" t="n">
         <v>119.01</v>
       </c>
-      <c r="K7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O7" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P7" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K7" s="5" t="n"/>
+      <c r="L7" s="5" t="n"/>
+      <c r="M7" s="5" t="n"/>
+      <c r="N7" s="5" t="n"/>
+      <c r="O7" s="5" t="n"/>
+      <c r="P7" s="5" t="n"/>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>D0=115.58; 最新=2026-06-03; 相对D0=2.97%; 本次触发=2026-06-03(正式买入); 历史重复2次; 重复日期=2026-06-02, 2026-06-03</t>
@@ -1015,24 +931,6 @@
       <c r="J8" t="n">
         <v>69.14</v>
       </c>
-      <c r="K8" t="n">
-        <v/>
-      </c>
-      <c r="L8" t="n">
-        <v/>
-      </c>
-      <c r="M8" t="n">
-        <v/>
-      </c>
-      <c r="N8" t="n">
-        <v/>
-      </c>
-      <c r="O8" t="n">
-        <v/>
-      </c>
-      <c r="P8" t="n">
-        <v/>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
           <t>D0=69.57; 最新=2026-06-03; 相对D0=-0.62%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1084,24 +982,12 @@
       <c r="J9" s="5" t="n">
         <v>40.93</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=40.13; 最新=2026-06-03; 相对D0=1.99%; 本次触发=2026-06-03(正式买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1153,24 +1039,12 @@
       <c r="J10" s="5" t="n">
         <v>31.326</v>
       </c>
-      <c r="K10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O10" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P10" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K10" s="5" t="n"/>
+      <c r="L10" s="5" t="n"/>
+      <c r="M10" s="5" t="n"/>
+      <c r="N10" s="5" t="n"/>
+      <c r="O10" s="5" t="n"/>
+      <c r="P10" s="5" t="n"/>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>D0=25.86; 最新=2026-06-03; 相对D0=21.14%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1222,24 +1096,6 @@
       <c r="J11" t="n">
         <v>266</v>
       </c>
-      <c r="K11" t="n">
-        <v/>
-      </c>
-      <c r="L11" t="n">
-        <v/>
-      </c>
-      <c r="M11" t="n">
-        <v/>
-      </c>
-      <c r="N11" t="n">
-        <v/>
-      </c>
-      <c r="O11" t="n">
-        <v/>
-      </c>
-      <c r="P11" t="n">
-        <v/>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
           <t>D0=274.71; 最新=2026-06-03; 相对D0=-3.17%; 本次触发=2026-06-03(预警买入); 历史重复1次; 重复日期=2026-06-03</t>
@@ -1291,24 +1147,6 @@
       <c r="J12" t="n">
         <v>281.795</v>
       </c>
-      <c r="K12" t="n">
-        <v/>
-      </c>
-      <c r="L12" t="n">
-        <v/>
-      </c>
-      <c r="M12" t="n">
-        <v/>
-      </c>
-      <c r="N12" t="n">
-        <v/>
-      </c>
-      <c r="O12" t="n">
-        <v/>
-      </c>
-      <c r="P12" t="n">
-        <v/>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
           <t>D0=281.80; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1360,24 +1198,6 @@
       <c r="J13" t="n">
         <v>116.72</v>
       </c>
-      <c r="K13" t="n">
-        <v/>
-      </c>
-      <c r="L13" t="n">
-        <v/>
-      </c>
-      <c r="M13" t="n">
-        <v/>
-      </c>
-      <c r="N13" t="n">
-        <v/>
-      </c>
-      <c r="O13" t="n">
-        <v/>
-      </c>
-      <c r="P13" t="n">
-        <v/>
-      </c>
       <c r="Q13" t="inlineStr">
         <is>
           <t>D0=116.72; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1429,24 +1249,12 @@
       <c r="J14" s="5" t="n">
         <v>119.01</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=119.01; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入)</t>
@@ -1498,24 +1306,6 @@
       <c r="J15" t="n">
         <v>122.47</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=122.47; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1567,24 +1357,12 @@
       <c r="J16" s="5" t="n">
         <v>40.93</v>
       </c>
-      <c r="K16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O16" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P16" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K16" s="5" t="n"/>
+      <c r="L16" s="5" t="n"/>
+      <c r="M16" s="5" t="n"/>
+      <c r="N16" s="5" t="n"/>
+      <c r="O16" s="5" t="n"/>
+      <c r="P16" s="5" t="n"/>
       <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>D0=40.93; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入)</t>
@@ -1636,24 +1414,6 @@
       <c r="J17" t="n">
         <v>50.38</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=50.38; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1705,24 +1465,6 @@
       <c r="J18" t="n">
         <v>507.75</v>
       </c>
-      <c r="K18" t="n">
-        <v/>
-      </c>
-      <c r="L18" t="n">
-        <v/>
-      </c>
-      <c r="M18" t="n">
-        <v/>
-      </c>
-      <c r="N18" t="n">
-        <v/>
-      </c>
-      <c r="O18" t="n">
-        <v/>
-      </c>
-      <c r="P18" t="n">
-        <v/>
-      </c>
       <c r="Q18" t="inlineStr">
         <is>
           <t>D0=507.75; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1774,24 +1516,6 @@
       <c r="J19" t="n">
         <v>617.7</v>
       </c>
-      <c r="K19" t="n">
-        <v/>
-      </c>
-      <c r="L19" t="n">
-        <v/>
-      </c>
-      <c r="M19" t="n">
-        <v/>
-      </c>
-      <c r="N19" t="n">
-        <v/>
-      </c>
-      <c r="O19" t="n">
-        <v/>
-      </c>
-      <c r="P19" t="n">
-        <v/>
-      </c>
       <c r="Q19" t="inlineStr">
         <is>
           <t>D0=617.70; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1843,24 +1567,6 @@
       <c r="J20" t="n">
         <v>80.5569</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=80.56; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -1912,24 +1618,6 @@
       <c r="J21" t="n">
         <v>23.435</v>
       </c>
-      <c r="K21" t="n">
-        <v/>
-      </c>
-      <c r="L21" t="n">
-        <v/>
-      </c>
-      <c r="M21" t="n">
-        <v/>
-      </c>
-      <c r="N21" t="n">
-        <v/>
-      </c>
-      <c r="O21" t="n">
-        <v/>
-      </c>
-      <c r="P21" t="n">
-        <v/>
-      </c>
       <c r="Q21" t="inlineStr">
         <is>
           <t>D0=23.43; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -1981,24 +1669,6 @@
       <c r="J22" t="n">
         <v>69.14</v>
       </c>
-      <c r="K22" t="n">
-        <v/>
-      </c>
-      <c r="L22" t="n">
-        <v/>
-      </c>
-      <c r="M22" t="n">
-        <v/>
-      </c>
-      <c r="N22" t="n">
-        <v/>
-      </c>
-      <c r="O22" t="n">
-        <v/>
-      </c>
-      <c r="P22" t="n">
-        <v/>
-      </c>
       <c r="Q22" t="inlineStr">
         <is>
           <t>D0=69.14; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2050,24 +1720,12 @@
       <c r="J23" s="5" t="n">
         <v>31.326</v>
       </c>
-      <c r="K23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O23" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P23" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K23" s="5" t="n"/>
+      <c r="L23" s="5" t="n"/>
+      <c r="M23" s="5" t="n"/>
+      <c r="N23" s="5" t="n"/>
+      <c r="O23" s="5" t="n"/>
+      <c r="P23" s="5" t="n"/>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>D0=31.33; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2119,24 +1777,6 @@
       <c r="J24" t="n">
         <v>92.12</v>
       </c>
-      <c r="K24" t="n">
-        <v/>
-      </c>
-      <c r="L24" t="n">
-        <v/>
-      </c>
-      <c r="M24" t="n">
-        <v/>
-      </c>
-      <c r="N24" t="n">
-        <v/>
-      </c>
-      <c r="O24" t="n">
-        <v/>
-      </c>
-      <c r="P24" t="n">
-        <v/>
-      </c>
       <c r="Q24" t="inlineStr">
         <is>
           <t>D0=92.12; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2188,24 +1828,6 @@
       <c r="J25" t="n">
         <v>266</v>
       </c>
-      <c r="K25" t="n">
-        <v/>
-      </c>
-      <c r="L25" t="n">
-        <v/>
-      </c>
-      <c r="M25" t="n">
-        <v/>
-      </c>
-      <c r="N25" t="n">
-        <v/>
-      </c>
-      <c r="O25" t="n">
-        <v/>
-      </c>
-      <c r="P25" t="n">
-        <v/>
-      </c>
       <c r="Q25" t="inlineStr">
         <is>
           <t>D0=266.00; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警买入)</t>
@@ -2257,24 +1879,6 @@
       <c r="J26" t="n">
         <v>383.8</v>
       </c>
-      <c r="K26" t="n">
-        <v/>
-      </c>
-      <c r="L26" t="n">
-        <v/>
-      </c>
-      <c r="M26" t="n">
-        <v/>
-      </c>
-      <c r="N26" t="n">
-        <v/>
-      </c>
-      <c r="O26" t="n">
-        <v/>
-      </c>
-      <c r="P26" t="n">
-        <v/>
-      </c>
       <c r="Q26" t="inlineStr">
         <is>
           <t>D0=383.80; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式买入 | 预警买入)</t>
@@ -2326,24 +1930,6 @@
       <c r="J27" t="n">
         <v>181.855</v>
       </c>
-      <c r="K27" t="n">
-        <v/>
-      </c>
-      <c r="L27" t="n">
-        <v/>
-      </c>
-      <c r="M27" t="n">
-        <v/>
-      </c>
-      <c r="N27" t="n">
-        <v/>
-      </c>
-      <c r="O27" t="n">
-        <v/>
-      </c>
-      <c r="P27" t="n">
-        <v/>
-      </c>
       <c r="Q27" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-06-03; 相对D0=0.20%; 历史重复2次; 重复日期=2026-05-27, 2026-06-01</t>
@@ -2395,24 +1981,12 @@
       <c r="J28" s="5" t="n">
         <v>186.49</v>
       </c>
-      <c r="K28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O28" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P28" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K28" s="5" t="n"/>
+      <c r="L28" s="5" t="n"/>
+      <c r="M28" s="5" t="n"/>
+      <c r="N28" s="5" t="n"/>
+      <c r="O28" s="5" t="n"/>
+      <c r="P28" s="5" t="n"/>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-06-03; 相对D0=-8.09%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -2464,24 +2038,12 @@
       <c r="J29" s="5" t="n">
         <v>183.13</v>
       </c>
-      <c r="K29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O29" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P29" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K29" s="5" t="n"/>
+      <c r="L29" s="5" t="n"/>
+      <c r="M29" s="5" t="n"/>
+      <c r="N29" s="5" t="n"/>
+      <c r="O29" s="5" t="n"/>
+      <c r="P29" s="5" t="n"/>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-06-03; 相对D0=9.42%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -2533,24 +2095,12 @@
       <c r="J30" s="5" t="n">
         <v>266.13</v>
       </c>
-      <c r="K30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O30" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P30" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K30" s="5" t="n"/>
+      <c r="L30" s="5" t="n"/>
+      <c r="M30" s="5" t="n"/>
+      <c r="N30" s="5" t="n"/>
+      <c r="O30" s="5" t="n"/>
+      <c r="P30" s="5" t="n"/>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>D0=294.07; 最新=2026-06-03; 相对D0=-9.50%; 历史重复1次; 重复日期=2026-05-29</t>
@@ -2602,24 +2152,12 @@
       <c r="J31" s="5" t="n">
         <v>56.1</v>
       </c>
-      <c r="K31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O31" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P31" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K31" s="5" t="n"/>
+      <c r="L31" s="5" t="n"/>
+      <c r="M31" s="5" t="n"/>
+      <c r="N31" s="5" t="n"/>
+      <c r="O31" s="5" t="n"/>
+      <c r="P31" s="5" t="n"/>
       <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-06-03; 相对D0=20.57%</t>
@@ -2671,24 +2209,6 @@
       <c r="J32" t="n">
         <v>16.315</v>
       </c>
-      <c r="K32" t="n">
-        <v/>
-      </c>
-      <c r="L32" t="n">
-        <v/>
-      </c>
-      <c r="M32" t="n">
-        <v/>
-      </c>
-      <c r="N32" t="n">
-        <v/>
-      </c>
-      <c r="O32" t="n">
-        <v/>
-      </c>
-      <c r="P32" t="n">
-        <v/>
-      </c>
       <c r="Q32" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-06-03; 相对D0=1.21%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -2740,24 +2260,12 @@
       <c r="J33" s="5" t="n">
         <v>192.09</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-06-03; 相对D0=6.68%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -2809,24 +2317,12 @@
       <c r="J34" s="5" t="n">
         <v>48.21</v>
       </c>
-      <c r="K34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O34" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P34" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K34" s="5" t="n"/>
+      <c r="L34" s="5" t="n"/>
+      <c r="M34" s="5" t="n"/>
+      <c r="N34" s="5" t="n"/>
+      <c r="O34" s="5" t="n"/>
+      <c r="P34" s="5" t="n"/>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-06-03; 相对D0=0.19%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -2878,24 +2374,12 @@
       <c r="J35" s="5" t="n">
         <v>140.75</v>
       </c>
-      <c r="K35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O35" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P35" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K35" s="5" t="n"/>
+      <c r="L35" s="5" t="n"/>
+      <c r="M35" s="5" t="n"/>
+      <c r="N35" s="5" t="n"/>
+      <c r="O35" s="5" t="n"/>
+      <c r="P35" s="5" t="n"/>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>D0=135.28; 最新=2026-06-03; 相对D0=4.04%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -2947,24 +2431,12 @@
       <c r="J36" s="5" t="n">
         <v>142.12</v>
       </c>
-      <c r="K36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O36" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P36" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K36" s="5" t="n"/>
+      <c r="L36" s="5" t="n"/>
+      <c r="M36" s="5" t="n"/>
+      <c r="N36" s="5" t="n"/>
+      <c r="O36" s="5" t="n"/>
+      <c r="P36" s="5" t="n"/>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-06-03; 相对D0=0.64%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -3016,24 +2488,12 @@
       <c r="J37" s="5" t="n">
         <v>419.695</v>
       </c>
-      <c r="K37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O37" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P37" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K37" s="5" t="n"/>
+      <c r="L37" s="5" t="n"/>
+      <c r="M37" s="5" t="n"/>
+      <c r="N37" s="5" t="n"/>
+      <c r="O37" s="5" t="n"/>
+      <c r="P37" s="5" t="n"/>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-06-03; 相对D0=7.24%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3085,24 +2545,12 @@
       <c r="J38" s="5" t="n">
         <v>968.13</v>
       </c>
-      <c r="K38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O38" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P38" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K38" s="5" t="n"/>
+      <c r="L38" s="5" t="n"/>
+      <c r="M38" s="5" t="n"/>
+      <c r="N38" s="5" t="n"/>
+      <c r="O38" s="5" t="n"/>
+      <c r="P38" s="5" t="n"/>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-06-03; 相对D0=-6.80%; 历史重复1次; 重复日期=2026-05-26</t>
@@ -3154,24 +2602,12 @@
       <c r="J39" s="5" t="n">
         <v>182.975</v>
       </c>
-      <c r="K39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O39" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P39" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K39" s="5" t="n"/>
+      <c r="L39" s="5" t="n"/>
+      <c r="M39" s="5" t="n"/>
+      <c r="N39" s="5" t="n"/>
+      <c r="O39" s="5" t="n"/>
+      <c r="P39" s="5" t="n"/>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-06-03; 相对D0=2.02%; 历史重复3次; 重复日期=2026-05-26, 2026-05-28, 2026-06-01</t>
@@ -3223,24 +2659,12 @@
       <c r="J40" s="5" t="n">
         <v>370.05</v>
       </c>
-      <c r="K40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O40" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P40" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K40" s="5" t="n"/>
+      <c r="L40" s="5" t="n"/>
+      <c r="M40" s="5" t="n"/>
+      <c r="N40" s="5" t="n"/>
+      <c r="O40" s="5" t="n"/>
+      <c r="P40" s="5" t="n"/>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-06-03; 相对D0=13.47%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -3292,24 +2716,12 @@
       <c r="J41" s="5" t="n">
         <v>25.8502</v>
       </c>
-      <c r="K41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O41" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P41" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K41" s="5" t="n"/>
+      <c r="L41" s="5" t="n"/>
+      <c r="M41" s="5" t="n"/>
+      <c r="N41" s="5" t="n"/>
+      <c r="O41" s="5" t="n"/>
+      <c r="P41" s="5" t="n"/>
       <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>D0=26.73; 最新=2026-06-03; 相对D0=-3.29%</t>
@@ -3361,24 +2773,12 @@
       <c r="J42" s="5" t="n">
         <v>133.145</v>
       </c>
-      <c r="K42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O42" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P42" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K42" s="5" t="n"/>
+      <c r="L42" s="5" t="n"/>
+      <c r="M42" s="5" t="n"/>
+      <c r="N42" s="5" t="n"/>
+      <c r="O42" s="5" t="n"/>
+      <c r="P42" s="5" t="n"/>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>D0=137.65; 最新=2026-06-03; 相对D0=-3.27%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -3430,24 +2830,6 @@
       <c r="J43" t="n">
         <v>258.05</v>
       </c>
-      <c r="K43" t="n">
-        <v/>
-      </c>
-      <c r="L43" t="n">
-        <v/>
-      </c>
-      <c r="M43" t="n">
-        <v/>
-      </c>
-      <c r="N43" t="n">
-        <v/>
-      </c>
-      <c r="O43" t="n">
-        <v/>
-      </c>
-      <c r="P43" t="n">
-        <v/>
-      </c>
       <c r="Q43" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-06-03; 相对D0=11.23%</t>
@@ -3499,24 +2881,6 @@
       <c r="J44" t="n">
         <v>144.34</v>
       </c>
-      <c r="K44" t="n">
-        <v/>
-      </c>
-      <c r="L44" t="n">
-        <v/>
-      </c>
-      <c r="M44" t="n">
-        <v/>
-      </c>
-      <c r="N44" t="n">
-        <v/>
-      </c>
-      <c r="O44" t="n">
-        <v/>
-      </c>
-      <c r="P44" t="n">
-        <v/>
-      </c>
       <c r="Q44" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-06-03; 相对D0=10.61%</t>
@@ -3568,24 +2932,12 @@
       <c r="J45" s="5" t="n">
         <v>276.67</v>
       </c>
-      <c r="K45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O45" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P45" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K45" s="5" t="n"/>
+      <c r="L45" s="5" t="n"/>
+      <c r="M45" s="5" t="n"/>
+      <c r="N45" s="5" t="n"/>
+      <c r="O45" s="5" t="n"/>
+      <c r="P45" s="5" t="n"/>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-06-03; 相对D0=5.50%; 历史重复3次; 重复日期=2026-05-26, 2026-05-27, 2026-06-02</t>
@@ -3637,24 +2989,12 @@
       <c r="J46" s="5" t="n">
         <v>60.075</v>
       </c>
-      <c r="K46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O46" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P46" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K46" s="5" t="n"/>
+      <c r="L46" s="5" t="n"/>
+      <c r="M46" s="5" t="n"/>
+      <c r="N46" s="5" t="n"/>
+      <c r="O46" s="5" t="n"/>
+      <c r="P46" s="5" t="n"/>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>D0=58.81; 最新=2026-06-03; 相对D0=2.15%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -3706,24 +3046,6 @@
       <c r="J47" t="n">
         <v>57.25</v>
       </c>
-      <c r="K47" t="n">
-        <v/>
-      </c>
-      <c r="L47" t="n">
-        <v/>
-      </c>
-      <c r="M47" t="n">
-        <v/>
-      </c>
-      <c r="N47" t="n">
-        <v/>
-      </c>
-      <c r="O47" t="n">
-        <v/>
-      </c>
-      <c r="P47" t="n">
-        <v/>
-      </c>
       <c r="Q47" t="inlineStr">
         <is>
           <t>D0=54.94; 最新=2026-06-03; 相对D0=4.20%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3775,24 +3097,6 @@
       <c r="J48" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="K48" t="n">
-        <v/>
-      </c>
-      <c r="L48" t="n">
-        <v/>
-      </c>
-      <c r="M48" t="n">
-        <v/>
-      </c>
-      <c r="N48" t="n">
-        <v/>
-      </c>
-      <c r="O48" t="n">
-        <v/>
-      </c>
-      <c r="P48" t="n">
-        <v/>
-      </c>
       <c r="Q48" t="inlineStr">
         <is>
           <t>D0=81.76; 最新=2026-06-03; 相对D0=7.14%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -3844,24 +3148,12 @@
       <c r="J49" s="5" t="n">
         <v>101.59</v>
       </c>
-      <c r="K49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O49" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P49" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K49" s="5" t="n"/>
+      <c r="L49" s="5" t="n"/>
+      <c r="M49" s="5" t="n"/>
+      <c r="N49" s="5" t="n"/>
+      <c r="O49" s="5" t="n"/>
+      <c r="P49" s="5" t="n"/>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-06-03; 相对D0=18.93%; 历史重复1次; 重复日期=2026-05-27</t>
@@ -3913,24 +3205,6 @@
       <c r="J50" t="n">
         <v>419.89</v>
       </c>
-      <c r="K50" t="n">
-        <v/>
-      </c>
-      <c r="L50" t="n">
-        <v/>
-      </c>
-      <c r="M50" t="n">
-        <v/>
-      </c>
-      <c r="N50" t="n">
-        <v/>
-      </c>
-      <c r="O50" t="n">
-        <v/>
-      </c>
-      <c r="P50" t="n">
-        <v/>
-      </c>
       <c r="Q50" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-06-03; 相对D0=-1.44%</t>
@@ -3982,24 +3256,12 @@
       <c r="J51" s="5" t="n">
         <v>14.22</v>
       </c>
-      <c r="K51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O51" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P51" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K51" s="5" t="n"/>
+      <c r="L51" s="5" t="n"/>
+      <c r="M51" s="5" t="n"/>
+      <c r="N51" s="5" t="n"/>
+      <c r="O51" s="5" t="n"/>
+      <c r="P51" s="5" t="n"/>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-06-03; 相对D0=9.22%; 历史重复3次; 重复日期=2026-05-26, 2026-05-29, 2026-06-02</t>
@@ -4051,24 +3313,12 @@
       <c r="J52" s="5" t="n">
         <v>153.41</v>
       </c>
-      <c r="K52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O52" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P52" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K52" s="5" t="n"/>
+      <c r="L52" s="5" t="n"/>
+      <c r="M52" s="5" t="n"/>
+      <c r="N52" s="5" t="n"/>
+      <c r="O52" s="5" t="n"/>
+      <c r="P52" s="5" t="n"/>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>D0=156.27; 最新=2026-06-03; 相对D0=-1.83%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -4120,24 +3370,6 @@
       <c r="J53" t="n">
         <v>51.675</v>
       </c>
-      <c r="K53" t="n">
-        <v/>
-      </c>
-      <c r="L53" t="n">
-        <v/>
-      </c>
-      <c r="M53" t="n">
-        <v/>
-      </c>
-      <c r="N53" t="n">
-        <v/>
-      </c>
-      <c r="O53" t="n">
-        <v/>
-      </c>
-      <c r="P53" t="n">
-        <v/>
-      </c>
       <c r="Q53" t="inlineStr">
         <is>
           <t>D0=50.29; 最新=2026-06-03; 相对D0=2.75%; 历史重复2次; 重复日期=2026-05-26, 2026-06-02</t>
@@ -4189,24 +3421,12 @@
       <c r="J54" s="5" t="n">
         <v>75.97</v>
       </c>
-      <c r="K54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O54" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P54" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K54" s="5" t="n"/>
+      <c r="L54" s="5" t="n"/>
+      <c r="M54" s="5" t="n"/>
+      <c r="N54" s="5" t="n"/>
+      <c r="O54" s="5" t="n"/>
+      <c r="P54" s="5" t="n"/>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>D0=73.46; 最新=2026-06-03; 相对D0=3.42%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -4258,24 +3478,6 @@
       <c r="J55" t="n">
         <v>484.33</v>
       </c>
-      <c r="K55" t="n">
-        <v/>
-      </c>
-      <c r="L55" t="n">
-        <v/>
-      </c>
-      <c r="M55" t="n">
-        <v/>
-      </c>
-      <c r="N55" t="n">
-        <v/>
-      </c>
-      <c r="O55" t="n">
-        <v/>
-      </c>
-      <c r="P55" t="n">
-        <v/>
-      </c>
       <c r="Q55" t="inlineStr">
         <is>
           <t>D0=422.01; 最新=2026-06-03; 相对D0=14.77%</t>
@@ -4327,24 +3529,6 @@
       <c r="J56" t="n">
         <v>91.16</v>
       </c>
-      <c r="K56" t="n">
-        <v/>
-      </c>
-      <c r="L56" t="n">
-        <v/>
-      </c>
-      <c r="M56" t="n">
-        <v/>
-      </c>
-      <c r="N56" t="n">
-        <v/>
-      </c>
-      <c r="O56" t="n">
-        <v/>
-      </c>
-      <c r="P56" t="n">
-        <v/>
-      </c>
       <c r="Q56" t="inlineStr">
         <is>
           <t>D0=86.49; 最新=2026-06-03; 相对D0=5.40%</t>
@@ -4396,24 +3580,12 @@
       <c r="J57" s="5" t="n">
         <v>186.49</v>
       </c>
-      <c r="K57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O57" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P57" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K57" s="5" t="n"/>
+      <c r="L57" s="5" t="n"/>
+      <c r="M57" s="5" t="n"/>
+      <c r="N57" s="5" t="n"/>
+      <c r="O57" s="5" t="n"/>
+      <c r="P57" s="5" t="n"/>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>D0=204.38; 最新=2026-06-03; 相对D0=-8.75%</t>
@@ -4465,24 +3637,12 @@
       <c r="J58" s="5" t="n">
         <v>183.13</v>
       </c>
-      <c r="K58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O58" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P58" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K58" s="5" t="n"/>
+      <c r="L58" s="5" t="n"/>
+      <c r="M58" s="5" t="n"/>
+      <c r="N58" s="5" t="n"/>
+      <c r="O58" s="5" t="n"/>
+      <c r="P58" s="5" t="n"/>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>D0=174.73; 最新=2026-06-03; 相对D0=4.81%</t>
@@ -4534,24 +3694,12 @@
       <c r="J59" s="5" t="n">
         <v>114.805</v>
       </c>
-      <c r="K59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O59" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P59" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K59" s="5" t="n"/>
+      <c r="L59" s="5" t="n"/>
+      <c r="M59" s="5" t="n"/>
+      <c r="N59" s="5" t="n"/>
+      <c r="O59" s="5" t="n"/>
+      <c r="P59" s="5" t="n"/>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>D0=108.17; 最新=2026-06-03; 相对D0=6.13%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4603,24 +3751,6 @@
       <c r="J60" t="n">
         <v>111.9799</v>
       </c>
-      <c r="K60" t="n">
-        <v/>
-      </c>
-      <c r="L60" t="n">
-        <v/>
-      </c>
-      <c r="M60" t="n">
-        <v/>
-      </c>
-      <c r="N60" t="n">
-        <v/>
-      </c>
-      <c r="O60" t="n">
-        <v/>
-      </c>
-      <c r="P60" t="n">
-        <v/>
-      </c>
       <c r="Q60" t="inlineStr">
         <is>
           <t>D0=105.89; 最新=2026-06-03; 相对D0=5.75%; 历史重复2次; 重复日期=2026-05-28, 2026-05-29</t>
@@ -4672,24 +3802,12 @@
       <c r="J61" s="5" t="n">
         <v>48.21</v>
       </c>
-      <c r="K61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O61" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P61" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K61" s="5" t="n"/>
+      <c r="L61" s="5" t="n"/>
+      <c r="M61" s="5" t="n"/>
+      <c r="N61" s="5" t="n"/>
+      <c r="O61" s="5" t="n"/>
+      <c r="P61" s="5" t="n"/>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>D0=49.46; 最新=2026-06-03; 相对D0=-2.53%</t>
@@ -4741,24 +3859,12 @@
       <c r="J62" s="5" t="n">
         <v>419.695</v>
       </c>
-      <c r="K62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O62" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P62" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K62" s="5" t="n"/>
+      <c r="L62" s="5" t="n"/>
+      <c r="M62" s="5" t="n"/>
+      <c r="N62" s="5" t="n"/>
+      <c r="O62" s="5" t="n"/>
+      <c r="P62" s="5" t="n"/>
       <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>D0=403.13; 最新=2026-06-03; 相对D0=4.11%</t>
@@ -4810,24 +3916,12 @@
       <c r="J63" s="5" t="n">
         <v>968.13</v>
       </c>
-      <c r="K63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O63" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P63" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K63" s="5" t="n"/>
+      <c r="L63" s="5" t="n"/>
+      <c r="M63" s="5" t="n"/>
+      <c r="N63" s="5" t="n"/>
+      <c r="O63" s="5" t="n"/>
+      <c r="P63" s="5" t="n"/>
       <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>D0=1070.47; 最新=2026-06-03; 相对D0=-9.56%</t>
@@ -4879,24 +3973,6 @@
       <c r="J64" t="n">
         <v>361.405</v>
       </c>
-      <c r="K64" t="n">
-        <v/>
-      </c>
-      <c r="L64" t="n">
-        <v/>
-      </c>
-      <c r="M64" t="n">
-        <v/>
-      </c>
-      <c r="N64" t="n">
-        <v/>
-      </c>
-      <c r="O64" t="n">
-        <v/>
-      </c>
-      <c r="P64" t="n">
-        <v/>
-      </c>
       <c r="Q64" t="inlineStr">
         <is>
           <t>D0=388.88; 最新=2026-06-03; 相对D0=-7.07%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -4948,24 +4024,12 @@
       <c r="J65" s="5" t="n">
         <v>182.975</v>
       </c>
-      <c r="K65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O65" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P65" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K65" s="5" t="n"/>
+      <c r="L65" s="5" t="n"/>
+      <c r="M65" s="5" t="n"/>
+      <c r="N65" s="5" t="n"/>
+      <c r="O65" s="5" t="n"/>
+      <c r="P65" s="5" t="n"/>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>D0=183.36; 最新=2026-06-03; 相对D0=-0.21%</t>
@@ -5017,24 +4081,6 @@
       <c r="J66" t="n">
         <v>68.19</v>
       </c>
-      <c r="K66" t="n">
-        <v/>
-      </c>
-      <c r="L66" t="n">
-        <v/>
-      </c>
-      <c r="M66" t="n">
-        <v/>
-      </c>
-      <c r="N66" t="n">
-        <v/>
-      </c>
-      <c r="O66" t="n">
-        <v/>
-      </c>
-      <c r="P66" t="n">
-        <v/>
-      </c>
       <c r="Q66" t="inlineStr">
         <is>
           <t>D0=69.63; 最新=2026-06-03; 相对D0=-2.07%</t>
@@ -5086,24 +4132,6 @@
       <c r="J67" t="n">
         <v>617.7</v>
       </c>
-      <c r="K67" t="n">
-        <v/>
-      </c>
-      <c r="L67" t="n">
-        <v/>
-      </c>
-      <c r="M67" t="n">
-        <v/>
-      </c>
-      <c r="N67" t="n">
-        <v/>
-      </c>
-      <c r="O67" t="n">
-        <v/>
-      </c>
-      <c r="P67" t="n">
-        <v/>
-      </c>
       <c r="Q67" t="inlineStr">
         <is>
           <t>D0=612.34; 最新=2026-06-03; 相对D0=0.88%</t>
@@ -5155,24 +4183,6 @@
       <c r="J68" t="n">
         <v>23.435</v>
       </c>
-      <c r="K68" t="n">
-        <v/>
-      </c>
-      <c r="L68" t="n">
-        <v/>
-      </c>
-      <c r="M68" t="n">
-        <v/>
-      </c>
-      <c r="N68" t="n">
-        <v/>
-      </c>
-      <c r="O68" t="n">
-        <v/>
-      </c>
-      <c r="P68" t="n">
-        <v/>
-      </c>
       <c r="Q68" t="inlineStr">
         <is>
           <t>D0=22.62; 最新=2026-06-03; 相对D0=3.60%</t>
@@ -5224,24 +4234,12 @@
       <c r="J69" s="5" t="n">
         <v>131.92</v>
       </c>
-      <c r="K69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O69" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P69" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K69" s="5" t="n"/>
+      <c r="L69" s="5" t="n"/>
+      <c r="M69" s="5" t="n"/>
+      <c r="N69" s="5" t="n"/>
+      <c r="O69" s="5" t="n"/>
+      <c r="P69" s="5" t="n"/>
       <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>D0=134.61; 最新=2026-06-03; 相对D0=-2.00%; 历史重复2次; 重复日期=2026-05-28, 2026-06-02</t>
@@ -5293,24 +4291,12 @@
       <c r="J70" s="5" t="n">
         <v>65.47</v>
       </c>
-      <c r="K70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O70" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P70" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K70" s="5" t="n"/>
+      <c r="L70" s="5" t="n"/>
+      <c r="M70" s="5" t="n"/>
+      <c r="N70" s="5" t="n"/>
+      <c r="O70" s="5" t="n"/>
+      <c r="P70" s="5" t="n"/>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>D0=68.70; 最新=2026-06-03; 相对D0=-4.70%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5362,24 +4348,12 @@
       <c r="J71" s="5" t="n">
         <v>276.67</v>
       </c>
-      <c r="K71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O71" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P71" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K71" s="5" t="n"/>
+      <c r="L71" s="5" t="n"/>
+      <c r="M71" s="5" t="n"/>
+      <c r="N71" s="5" t="n"/>
+      <c r="O71" s="5" t="n"/>
+      <c r="P71" s="5" t="n"/>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>D0=274.17; 最新=2026-06-03; 相对D0=0.91%</t>
@@ -5431,24 +4405,6 @@
       <c r="J72" t="n">
         <v>57.25</v>
       </c>
-      <c r="K72" t="n">
-        <v/>
-      </c>
-      <c r="L72" t="n">
-        <v/>
-      </c>
-      <c r="M72" t="n">
-        <v/>
-      </c>
-      <c r="N72" t="n">
-        <v/>
-      </c>
-      <c r="O72" t="n">
-        <v/>
-      </c>
-      <c r="P72" t="n">
-        <v/>
-      </c>
       <c r="Q72" t="inlineStr">
         <is>
           <t>D0=56.31; 最新=2026-06-03; 相对D0=1.67%</t>
@@ -5500,24 +4456,6 @@
       <c r="J73" t="n">
         <v>108.38</v>
       </c>
-      <c r="K73" t="n">
-        <v/>
-      </c>
-      <c r="L73" t="n">
-        <v/>
-      </c>
-      <c r="M73" t="n">
-        <v/>
-      </c>
-      <c r="N73" t="n">
-        <v/>
-      </c>
-      <c r="O73" t="n">
-        <v/>
-      </c>
-      <c r="P73" t="n">
-        <v/>
-      </c>
       <c r="Q73" t="inlineStr">
         <is>
           <t>D0=106.94; 最新=2026-06-03; 相对D0=1.35%</t>
@@ -5569,24 +4507,12 @@
       <c r="J74" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="K74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O74" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P74" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K74" s="5" t="n"/>
+      <c r="L74" s="5" t="n"/>
+      <c r="M74" s="5" t="n"/>
+      <c r="N74" s="5" t="n"/>
+      <c r="O74" s="5" t="n"/>
+      <c r="P74" s="5" t="n"/>
       <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>D0=12.22; 最新=2026-06-03; 相对D0=-0.16%</t>
@@ -5638,24 +4564,6 @@
       <c r="J75" t="n">
         <v>16.705</v>
       </c>
-      <c r="K75" t="n">
-        <v/>
-      </c>
-      <c r="L75" t="n">
-        <v/>
-      </c>
-      <c r="M75" t="n">
-        <v/>
-      </c>
-      <c r="N75" t="n">
-        <v/>
-      </c>
-      <c r="O75" t="n">
-        <v/>
-      </c>
-      <c r="P75" t="n">
-        <v/>
-      </c>
       <c r="Q75" t="inlineStr">
         <is>
           <t>D0=15.98; 最新=2026-06-03; 相对D0=4.54%</t>
@@ -5707,24 +4615,6 @@
       <c r="J76" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="K76" t="n">
-        <v/>
-      </c>
-      <c r="L76" t="n">
-        <v/>
-      </c>
-      <c r="M76" t="n">
-        <v/>
-      </c>
-      <c r="N76" t="n">
-        <v/>
-      </c>
-      <c r="O76" t="n">
-        <v/>
-      </c>
-      <c r="P76" t="n">
-        <v/>
-      </c>
       <c r="Q76" t="inlineStr">
         <is>
           <t>D0=84.64; 最新=2026-06-03; 相对D0=3.50%</t>
@@ -5776,24 +4666,12 @@
       <c r="J77" s="5" t="n">
         <v>14.22</v>
       </c>
-      <c r="K77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O77" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P77" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K77" s="5" t="n"/>
+      <c r="L77" s="5" t="n"/>
+      <c r="M77" s="5" t="n"/>
+      <c r="N77" s="5" t="n"/>
+      <c r="O77" s="5" t="n"/>
+      <c r="P77" s="5" t="n"/>
       <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>D0=13.51; 最新=2026-06-03; 相对D0=5.26%</t>
@@ -5845,24 +4723,12 @@
       <c r="J78" s="5" t="n">
         <v>18.0707</v>
       </c>
-      <c r="K78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O78" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P78" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K78" s="5" t="n"/>
+      <c r="L78" s="5" t="n"/>
+      <c r="M78" s="5" t="n"/>
+      <c r="N78" s="5" t="n"/>
+      <c r="O78" s="5" t="n"/>
+      <c r="P78" s="5" t="n"/>
       <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>D0=18.40; 最新=2026-06-03; 相对D0=-1.79%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5914,24 +4780,6 @@
       <c r="J79" t="n">
         <v>333.79</v>
       </c>
-      <c r="K79" t="n">
-        <v/>
-      </c>
-      <c r="L79" t="n">
-        <v/>
-      </c>
-      <c r="M79" t="n">
-        <v/>
-      </c>
-      <c r="N79" t="n">
-        <v/>
-      </c>
-      <c r="O79" t="n">
-        <v/>
-      </c>
-      <c r="P79" t="n">
-        <v/>
-      </c>
       <c r="Q79" t="inlineStr">
         <is>
           <t>D0=323.91; 最新=2026-06-03; 相对D0=3.05%; 历史重复2次; 重复日期=2026-06-01, 2026-06-02</t>
@@ -5983,24 +4831,6 @@
       <c r="J80" t="n">
         <v>51.675</v>
       </c>
-      <c r="K80" t="n">
-        <v/>
-      </c>
-      <c r="L80" t="n">
-        <v/>
-      </c>
-      <c r="M80" t="n">
-        <v/>
-      </c>
-      <c r="N80" t="n">
-        <v/>
-      </c>
-      <c r="O80" t="n">
-        <v/>
-      </c>
-      <c r="P80" t="n">
-        <v/>
-      </c>
       <c r="Q80" t="inlineStr">
         <is>
           <t>D0=50.99; 最新=2026-06-03; 相对D0=1.34%</t>
@@ -6052,24 +4882,6 @@
       <c r="J81" t="n">
         <v>181.855</v>
       </c>
-      <c r="K81" t="n">
-        <v/>
-      </c>
-      <c r="L81" t="n">
-        <v/>
-      </c>
-      <c r="M81" t="n">
-        <v/>
-      </c>
-      <c r="N81" t="n">
-        <v/>
-      </c>
-      <c r="O81" t="n">
-        <v/>
-      </c>
-      <c r="P81" t="n">
-        <v/>
-      </c>
       <c r="Q81" t="inlineStr">
         <is>
           <t>D0=179.83; 最新=2026-06-03; 相对D0=1.13%</t>
@@ -6121,24 +4933,6 @@
       <c r="J82" t="n">
         <v>248.21</v>
       </c>
-      <c r="K82" t="n">
-        <v/>
-      </c>
-      <c r="L82" t="n">
-        <v/>
-      </c>
-      <c r="M82" t="n">
-        <v/>
-      </c>
-      <c r="N82" t="n">
-        <v/>
-      </c>
-      <c r="O82" t="n">
-        <v/>
-      </c>
-      <c r="P82" t="n">
-        <v/>
-      </c>
       <c r="Q82" t="inlineStr">
         <is>
           <t>D0=271.85; 最新=2026-06-03; 相对D0=-8.70%</t>
@@ -6159,7 +4953,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D83" t="inlineStr"/>
       <c r="E83" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6186,24 +4979,6 @@
       <c r="J83" t="n">
         <v>91.06</v>
       </c>
-      <c r="K83" t="n">
-        <v/>
-      </c>
-      <c r="L83" t="n">
-        <v/>
-      </c>
-      <c r="M83" t="n">
-        <v/>
-      </c>
-      <c r="N83" t="n">
-        <v/>
-      </c>
-      <c r="O83" t="n">
-        <v/>
-      </c>
-      <c r="P83" t="n">
-        <v/>
-      </c>
       <c r="Q83" t="inlineStr">
         <is>
           <t>D0=90.87; 最新=2026-06-03; 相对D0=0.21%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6255,24 +5030,6 @@
       <c r="J84" t="n">
         <v>16.315</v>
       </c>
-      <c r="K84" t="n">
-        <v/>
-      </c>
-      <c r="L84" t="n">
-        <v/>
-      </c>
-      <c r="M84" t="n">
-        <v/>
-      </c>
-      <c r="N84" t="n">
-        <v/>
-      </c>
-      <c r="O84" t="n">
-        <v/>
-      </c>
-      <c r="P84" t="n">
-        <v/>
-      </c>
       <c r="Q84" t="inlineStr">
         <is>
           <t>D0=16.46; 最新=2026-06-03; 相对D0=-0.88%</t>
@@ -6324,24 +5081,6 @@
       <c r="J85" t="n">
         <v>26.735</v>
       </c>
-      <c r="K85" t="n">
-        <v/>
-      </c>
-      <c r="L85" t="n">
-        <v/>
-      </c>
-      <c r="M85" t="n">
-        <v/>
-      </c>
-      <c r="N85" t="n">
-        <v/>
-      </c>
-      <c r="O85" t="n">
-        <v/>
-      </c>
-      <c r="P85" t="n">
-        <v/>
-      </c>
       <c r="Q85" t="inlineStr">
         <is>
           <t>D0=25.20; 最新=2026-06-03; 相对D0=6.09%</t>
@@ -6393,24 +5132,6 @@
       <c r="J86" t="n">
         <v>83.625</v>
       </c>
-      <c r="K86" t="n">
-        <v/>
-      </c>
-      <c r="L86" t="n">
-        <v/>
-      </c>
-      <c r="M86" t="n">
-        <v/>
-      </c>
-      <c r="N86" t="n">
-        <v/>
-      </c>
-      <c r="O86" t="n">
-        <v/>
-      </c>
-      <c r="P86" t="n">
-        <v/>
-      </c>
       <c r="Q86" t="inlineStr">
         <is>
           <t>D0=76.23; 最新=2026-06-03; 相对D0=9.70%; 历史重复1次; 重复日期=2026-05-28</t>
@@ -6462,24 +5183,6 @@
       <c r="J87" t="n">
         <v>50.38</v>
       </c>
-      <c r="K87" t="n">
-        <v/>
-      </c>
-      <c r="L87" t="n">
-        <v/>
-      </c>
-      <c r="M87" t="n">
-        <v/>
-      </c>
-      <c r="N87" t="n">
-        <v/>
-      </c>
-      <c r="O87" t="n">
-        <v/>
-      </c>
-      <c r="P87" t="n">
-        <v/>
-      </c>
       <c r="Q87" t="inlineStr">
         <is>
           <t>D0=50.44; 最新=2026-06-03; 相对D0=-0.12%</t>
@@ -6531,24 +5234,12 @@
       <c r="J88" s="5" t="n">
         <v>119.66</v>
       </c>
-      <c r="K88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O88" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P88" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K88" s="5" t="n"/>
+      <c r="L88" s="5" t="n"/>
+      <c r="M88" s="5" t="n"/>
+      <c r="N88" s="5" t="n"/>
+      <c r="O88" s="5" t="n"/>
+      <c r="P88" s="5" t="n"/>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>D0=102.12; 最新=2026-06-03; 相对D0=17.18%</t>
@@ -6600,24 +5291,12 @@
       <c r="J89" s="5" t="n">
         <v>276.67</v>
       </c>
-      <c r="K89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O89" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P89" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K89" s="5" t="n"/>
+      <c r="L89" s="5" t="n"/>
+      <c r="M89" s="5" t="n"/>
+      <c r="N89" s="5" t="n"/>
+      <c r="O89" s="5" t="n"/>
+      <c r="P89" s="5" t="n"/>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>D0=266.89; 最新=2026-06-03; 相对D0=3.66%</t>
@@ -6669,24 +5348,6 @@
       <c r="J90" t="n">
         <v>228.945</v>
       </c>
-      <c r="K90" t="n">
-        <v/>
-      </c>
-      <c r="L90" t="n">
-        <v/>
-      </c>
-      <c r="M90" t="n">
-        <v/>
-      </c>
-      <c r="N90" t="n">
-        <v/>
-      </c>
-      <c r="O90" t="n">
-        <v/>
-      </c>
-      <c r="P90" t="n">
-        <v/>
-      </c>
       <c r="Q90" t="inlineStr">
         <is>
           <t>D0=190.96; 最新=2026-06-03; 相对D0=19.89%</t>
@@ -6738,24 +5399,12 @@
       <c r="J91" s="5" t="n">
         <v>101.59</v>
       </c>
-      <c r="K91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O91" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P91" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K91" s="5" t="n"/>
+      <c r="L91" s="5" t="n"/>
+      <c r="M91" s="5" t="n"/>
+      <c r="N91" s="5" t="n"/>
+      <c r="O91" s="5" t="n"/>
+      <c r="P91" s="5" t="n"/>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>D0=89.07; 最新=2026-06-03; 相对D0=14.06%</t>
@@ -6807,24 +5456,6 @@
       <c r="J92" t="n">
         <v>383.8</v>
       </c>
-      <c r="K92" t="n">
-        <v/>
-      </c>
-      <c r="L92" t="n">
-        <v/>
-      </c>
-      <c r="M92" t="n">
-        <v/>
-      </c>
-      <c r="N92" t="n">
-        <v/>
-      </c>
-      <c r="O92" t="n">
-        <v/>
-      </c>
-      <c r="P92" t="n">
-        <v/>
-      </c>
       <c r="Q92" t="inlineStr">
         <is>
           <t>D0=384.01; 最新=2026-06-03; 相对D0=-0.05%</t>
@@ -6876,24 +5507,6 @@
       <c r="J93" t="n">
         <v>284.4836</v>
       </c>
-      <c r="K93" t="n">
-        <v/>
-      </c>
-      <c r="L93" t="n">
-        <v/>
-      </c>
-      <c r="M93" t="n">
-        <v/>
-      </c>
-      <c r="N93" t="n">
-        <v/>
-      </c>
-      <c r="O93" t="n">
-        <v/>
-      </c>
-      <c r="P93" t="n">
-        <v/>
-      </c>
       <c r="Q93" t="inlineStr">
         <is>
           <t>D0=290.01; 最新=2026-06-03; 相对D0=-1.91%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -6914,7 +5527,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
       <c r="E94" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -6941,24 +5553,6 @@
       <c r="J94" t="n">
         <v>91.06</v>
       </c>
-      <c r="K94" t="n">
-        <v/>
-      </c>
-      <c r="L94" t="n">
-        <v/>
-      </c>
-      <c r="M94" t="n">
-        <v/>
-      </c>
-      <c r="N94" t="n">
-        <v/>
-      </c>
-      <c r="O94" t="n">
-        <v/>
-      </c>
-      <c r="P94" t="n">
-        <v/>
-      </c>
       <c r="Q94" t="inlineStr">
         <is>
           <t>D0=91.09; 最新=2026-06-03; 相对D0=-0.03%</t>
@@ -7010,24 +5604,12 @@
       <c r="J95" s="5" t="n">
         <v>114.805</v>
       </c>
-      <c r="K95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O95" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P95" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K95" s="5" t="n"/>
+      <c r="L95" s="5" t="n"/>
+      <c r="M95" s="5" t="n"/>
+      <c r="N95" s="5" t="n"/>
+      <c r="O95" s="5" t="n"/>
+      <c r="P95" s="5" t="n"/>
       <c r="Q95" s="5" t="inlineStr">
         <is>
           <t>D0=110.63; 最新=2026-06-03; 相对D0=3.77%</t>
@@ -7079,24 +5661,6 @@
       <c r="J96" t="n">
         <v>91.7</v>
       </c>
-      <c r="K96" t="n">
-        <v/>
-      </c>
-      <c r="L96" t="n">
-        <v/>
-      </c>
-      <c r="M96" t="n">
-        <v/>
-      </c>
-      <c r="N96" t="n">
-        <v/>
-      </c>
-      <c r="O96" t="n">
-        <v/>
-      </c>
-      <c r="P96" t="n">
-        <v/>
-      </c>
       <c r="Q96" t="inlineStr">
         <is>
           <t>D0=83.68; 最新=2026-06-03; 相对D0=9.58%</t>
@@ -7148,24 +5712,12 @@
       <c r="J97" s="5" t="n">
         <v>192.09</v>
       </c>
-      <c r="K97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O97" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P97" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K97" s="5" t="n"/>
+      <c r="L97" s="5" t="n"/>
+      <c r="M97" s="5" t="n"/>
+      <c r="N97" s="5" t="n"/>
+      <c r="O97" s="5" t="n"/>
+      <c r="P97" s="5" t="n"/>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>D0=176.17; 最新=2026-06-03; 相对D0=9.04%</t>
@@ -7217,24 +5769,6 @@
       <c r="J98" t="n">
         <v>747.465</v>
       </c>
-      <c r="K98" t="n">
-        <v/>
-      </c>
-      <c r="L98" t="n">
-        <v/>
-      </c>
-      <c r="M98" t="n">
-        <v/>
-      </c>
-      <c r="N98" t="n">
-        <v/>
-      </c>
-      <c r="O98" t="n">
-        <v/>
-      </c>
-      <c r="P98" t="n">
-        <v/>
-      </c>
       <c r="Q98" t="inlineStr">
         <is>
           <t>D0=671.00; 最新=2026-06-03; 相对D0=11.40%</t>
@@ -7286,24 +5820,6 @@
       <c r="J99" t="n">
         <v>111.9799</v>
       </c>
-      <c r="K99" t="n">
-        <v/>
-      </c>
-      <c r="L99" t="n">
-        <v/>
-      </c>
-      <c r="M99" t="n">
-        <v/>
-      </c>
-      <c r="N99" t="n">
-        <v/>
-      </c>
-      <c r="O99" t="n">
-        <v/>
-      </c>
-      <c r="P99" t="n">
-        <v/>
-      </c>
       <c r="Q99" t="inlineStr">
         <is>
           <t>D0=106.86; 最新=2026-06-03; 相对D0=4.79%</t>
@@ -7355,24 +5871,6 @@
       <c r="J100" t="n">
         <v>66.3702</v>
       </c>
-      <c r="K100" t="n">
-        <v/>
-      </c>
-      <c r="L100" t="n">
-        <v/>
-      </c>
-      <c r="M100" t="n">
-        <v/>
-      </c>
-      <c r="N100" t="n">
-        <v/>
-      </c>
-      <c r="O100" t="n">
-        <v/>
-      </c>
-      <c r="P100" t="n">
-        <v/>
-      </c>
       <c r="Q100" t="inlineStr">
         <is>
           <t>D0=67.38; 最新=2026-06-03; 相对D0=-1.50%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -7393,7 +5891,6 @@
           <t>EQIX</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
       <c r="E101" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -7420,24 +5917,6 @@
       <c r="J101" t="n">
         <v>1089.045</v>
       </c>
-      <c r="K101" t="n">
-        <v/>
-      </c>
-      <c r="L101" t="n">
-        <v/>
-      </c>
-      <c r="M101" t="n">
-        <v/>
-      </c>
-      <c r="N101" t="n">
-        <v/>
-      </c>
-      <c r="O101" t="n">
-        <v/>
-      </c>
-      <c r="P101" t="n">
-        <v/>
-      </c>
       <c r="Q101" t="inlineStr">
         <is>
           <t>D0=1069.44; 最新=2026-06-03; 相对D0=1.83%</t>
@@ -7489,24 +5968,6 @@
       <c r="J102" t="n">
         <v>145.99</v>
       </c>
-      <c r="K102" t="n">
-        <v/>
-      </c>
-      <c r="L102" t="n">
-        <v/>
-      </c>
-      <c r="M102" t="n">
-        <v/>
-      </c>
-      <c r="N102" t="n">
-        <v/>
-      </c>
-      <c r="O102" t="n">
-        <v/>
-      </c>
-      <c r="P102" t="n">
-        <v/>
-      </c>
       <c r="Q102" t="inlineStr">
         <is>
           <t>D0=129.70; 最新=2026-06-03; 相对D0=12.56%</t>
@@ -7558,24 +6019,6 @@
       <c r="J103" t="n">
         <v>361.405</v>
       </c>
-      <c r="K103" t="n">
-        <v/>
-      </c>
-      <c r="L103" t="n">
-        <v/>
-      </c>
-      <c r="M103" t="n">
-        <v/>
-      </c>
-      <c r="N103" t="n">
-        <v/>
-      </c>
-      <c r="O103" t="n">
-        <v/>
-      </c>
-      <c r="P103" t="n">
-        <v/>
-      </c>
       <c r="Q103" t="inlineStr">
         <is>
           <t>D0=390.13; 最新=2026-06-03; 相对D0=-7.36%</t>
@@ -7627,24 +6070,6 @@
       <c r="J104" t="n">
         <v>83.625</v>
       </c>
-      <c r="K104" t="n">
-        <v/>
-      </c>
-      <c r="L104" t="n">
-        <v/>
-      </c>
-      <c r="M104" t="n">
-        <v/>
-      </c>
-      <c r="N104" t="n">
-        <v/>
-      </c>
-      <c r="O104" t="n">
-        <v/>
-      </c>
-      <c r="P104" t="n">
-        <v/>
-      </c>
       <c r="Q104" t="inlineStr">
         <is>
           <t>D0=84.84; 最新=2026-06-03; 相对D0=-1.43%</t>
@@ -7696,24 +6121,12 @@
       <c r="J105" s="5" t="n">
         <v>100.08</v>
       </c>
-      <c r="K105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O105" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P105" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K105" s="5" t="n"/>
+      <c r="L105" s="5" t="n"/>
+      <c r="M105" s="5" t="n"/>
+      <c r="N105" s="5" t="n"/>
+      <c r="O105" s="5" t="n"/>
+      <c r="P105" s="5" t="n"/>
       <c r="Q105" s="5" t="inlineStr">
         <is>
           <t>D0=95.68; 最新=2026-06-03; 相对D0=4.60%</t>
@@ -7765,24 +6178,12 @@
       <c r="J106" s="5" t="n">
         <v>182.975</v>
       </c>
-      <c r="K106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O106" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P106" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K106" s="5" t="n"/>
+      <c r="L106" s="5" t="n"/>
+      <c r="M106" s="5" t="n"/>
+      <c r="N106" s="5" t="n"/>
+      <c r="O106" s="5" t="n"/>
+      <c r="P106" s="5" t="n"/>
       <c r="Q106" s="5" t="inlineStr">
         <is>
           <t>D0=185.46; 最新=2026-06-03; 相对D0=-1.34%</t>
@@ -7834,24 +6235,12 @@
       <c r="J107" s="5" t="n">
         <v>370.05</v>
       </c>
-      <c r="K107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O107" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P107" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K107" s="5" t="n"/>
+      <c r="L107" s="5" t="n"/>
+      <c r="M107" s="5" t="n"/>
+      <c r="N107" s="5" t="n"/>
+      <c r="O107" s="5" t="n"/>
+      <c r="P107" s="5" t="n"/>
       <c r="Q107" s="5" t="inlineStr">
         <is>
           <t>D0=325.68; 最新=2026-06-03; 相对D0=13.62%</t>
@@ -7903,24 +6292,6 @@
       <c r="J108" t="n">
         <v>425.565</v>
       </c>
-      <c r="K108" t="n">
-        <v/>
-      </c>
-      <c r="L108" t="n">
-        <v/>
-      </c>
-      <c r="M108" t="n">
-        <v/>
-      </c>
-      <c r="N108" t="n">
-        <v/>
-      </c>
-      <c r="O108" t="n">
-        <v/>
-      </c>
-      <c r="P108" t="n">
-        <v/>
-      </c>
       <c r="Q108" t="inlineStr">
         <is>
           <t>D0=426.99; 最新=2026-06-03; 相对D0=-0.33%</t>
@@ -7972,24 +6343,6 @@
       <c r="J109" t="n">
         <v>249.71</v>
       </c>
-      <c r="K109" t="n">
-        <v/>
-      </c>
-      <c r="L109" t="n">
-        <v/>
-      </c>
-      <c r="M109" t="n">
-        <v/>
-      </c>
-      <c r="N109" t="n">
-        <v/>
-      </c>
-      <c r="O109" t="n">
-        <v/>
-      </c>
-      <c r="P109" t="n">
-        <v/>
-      </c>
       <c r="Q109" t="inlineStr">
         <is>
           <t>D0=226.34; 最新=2026-06-03; 相对D0=10.33%</t>
@@ -8041,24 +6394,12 @@
       <c r="J110" s="5" t="n">
         <v>131.92</v>
       </c>
-      <c r="K110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O110" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P110" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K110" s="5" t="n"/>
+      <c r="L110" s="5" t="n"/>
+      <c r="M110" s="5" t="n"/>
+      <c r="N110" s="5" t="n"/>
+      <c r="O110" s="5" t="n"/>
+      <c r="P110" s="5" t="n"/>
       <c r="Q110" s="5" t="inlineStr">
         <is>
           <t>D0=133.31; 最新=2026-06-03; 相对D0=-1.04%</t>
@@ -8110,24 +6451,6 @@
       <c r="J111" t="n">
         <v>124.51</v>
       </c>
-      <c r="K111" t="n">
-        <v/>
-      </c>
-      <c r="L111" t="n">
-        <v/>
-      </c>
-      <c r="M111" t="n">
-        <v/>
-      </c>
-      <c r="N111" t="n">
-        <v/>
-      </c>
-      <c r="O111" t="n">
-        <v/>
-      </c>
-      <c r="P111" t="n">
-        <v/>
-      </c>
       <c r="Q111" t="inlineStr">
         <is>
           <t>D0=94.72; 最新=2026-06-03; 相对D0=31.45%</t>
@@ -8179,24 +6502,6 @@
       <c r="J112" t="n">
         <v>278.6215</v>
       </c>
-      <c r="K112" t="n">
-        <v/>
-      </c>
-      <c r="L112" t="n">
-        <v/>
-      </c>
-      <c r="M112" t="n">
-        <v/>
-      </c>
-      <c r="N112" t="n">
-        <v/>
-      </c>
-      <c r="O112" t="n">
-        <v/>
-      </c>
-      <c r="P112" t="n">
-        <v/>
-      </c>
       <c r="Q112" t="inlineStr">
         <is>
           <t>D0=257.77; 最新=2026-06-03; 相对D0=8.09%</t>
@@ -8248,24 +6553,12 @@
       <c r="J113" s="5" t="n">
         <v>142.78</v>
       </c>
-      <c r="K113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O113" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P113" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K113" s="5" t="n"/>
+      <c r="L113" s="5" t="n"/>
+      <c r="M113" s="5" t="n"/>
+      <c r="N113" s="5" t="n"/>
+      <c r="O113" s="5" t="n"/>
+      <c r="P113" s="5" t="n"/>
       <c r="Q113" s="5" t="inlineStr">
         <is>
           <t>D0=143.34; 最新=2026-06-03; 相对D0=-0.39%</t>
@@ -8317,24 +6610,12 @@
       <c r="J114" s="5" t="n">
         <v>256.75</v>
       </c>
-      <c r="K114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O114" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P114" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K114" s="5" t="n"/>
+      <c r="L114" s="5" t="n"/>
+      <c r="M114" s="5" t="n"/>
+      <c r="N114" s="5" t="n"/>
+      <c r="O114" s="5" t="n"/>
+      <c r="P114" s="5" t="n"/>
       <c r="Q114" s="5" t="inlineStr">
         <is>
           <t>D0=259.21; 最新=2026-06-03; 相对D0=-0.95%</t>
@@ -8386,24 +6667,12 @@
       <c r="J115" s="5" t="n">
         <v>183.13</v>
       </c>
-      <c r="K115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O115" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P115" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K115" s="5" t="n"/>
+      <c r="L115" s="5" t="n"/>
+      <c r="M115" s="5" t="n"/>
+      <c r="N115" s="5" t="n"/>
+      <c r="O115" s="5" t="n"/>
+      <c r="P115" s="5" t="n"/>
       <c r="Q115" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-03; 相对D0=6.68%</t>
@@ -8455,24 +6724,12 @@
       <c r="J116" s="5" t="n">
         <v>266.13</v>
       </c>
-      <c r="K116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O116" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P116" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K116" s="5" t="n"/>
+      <c r="L116" s="5" t="n"/>
+      <c r="M116" s="5" t="n"/>
+      <c r="N116" s="5" t="n"/>
+      <c r="O116" s="5" t="n"/>
+      <c r="P116" s="5" t="n"/>
       <c r="Q116" s="5" t="inlineStr">
         <is>
           <t>D0=287.75; 最新=2026-06-03; 相对D0=-7.51%</t>
@@ -8524,24 +6781,6 @@
       <c r="J117" t="n">
         <v>165.5</v>
       </c>
-      <c r="K117" t="n">
-        <v/>
-      </c>
-      <c r="L117" t="n">
-        <v/>
-      </c>
-      <c r="M117" t="n">
-        <v/>
-      </c>
-      <c r="N117" t="n">
-        <v/>
-      </c>
-      <c r="O117" t="n">
-        <v/>
-      </c>
-      <c r="P117" t="n">
-        <v/>
-      </c>
       <c r="Q117" t="inlineStr">
         <is>
           <t>D0=189.03; 最新=2026-06-03; 相对D0=-12.45%</t>
@@ -8593,24 +6832,12 @@
       <c r="J118" s="5" t="n">
         <v>192.09</v>
       </c>
-      <c r="K118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O118" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P118" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K118" s="5" t="n"/>
+      <c r="L118" s="5" t="n"/>
+      <c r="M118" s="5" t="n"/>
+      <c r="N118" s="5" t="n"/>
+      <c r="O118" s="5" t="n"/>
+      <c r="P118" s="5" t="n"/>
       <c r="Q118" s="5" t="inlineStr">
         <is>
           <t>D0=191.10; 最新=2026-06-03; 相对D0=0.52%</t>
@@ -8662,24 +6889,6 @@
       <c r="J119" t="n">
         <v>111.9799</v>
       </c>
-      <c r="K119" t="n">
-        <v/>
-      </c>
-      <c r="L119" t="n">
-        <v/>
-      </c>
-      <c r="M119" t="n">
-        <v/>
-      </c>
-      <c r="N119" t="n">
-        <v/>
-      </c>
-      <c r="O119" t="n">
-        <v/>
-      </c>
-      <c r="P119" t="n">
-        <v/>
-      </c>
       <c r="Q119" t="inlineStr">
         <is>
           <t>D0=109.53; 最新=2026-06-03; 相对D0=2.24%</t>
@@ -8731,24 +6940,12 @@
       <c r="J120" s="5" t="n">
         <v>48.21</v>
       </c>
-      <c r="K120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O120" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P120" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K120" s="5" t="n"/>
+      <c r="L120" s="5" t="n"/>
+      <c r="M120" s="5" t="n"/>
+      <c r="N120" s="5" t="n"/>
+      <c r="O120" s="5" t="n"/>
+      <c r="P120" s="5" t="n"/>
       <c r="Q120" s="5" t="inlineStr">
         <is>
           <t>D0=48.42; 最新=2026-06-03; 相对D0=-0.43%</t>
@@ -8800,24 +6997,6 @@
       <c r="J121" t="n">
         <v>2109.05</v>
       </c>
-      <c r="K121" t="n">
-        <v/>
-      </c>
-      <c r="L121" t="n">
-        <v/>
-      </c>
-      <c r="M121" t="n">
-        <v/>
-      </c>
-      <c r="N121" t="n">
-        <v/>
-      </c>
-      <c r="O121" t="n">
-        <v/>
-      </c>
-      <c r="P121" t="n">
-        <v/>
-      </c>
       <c r="Q121" t="inlineStr">
         <is>
           <t>D0=1921.71; 最新=2026-06-03; 相对D0=9.75%</t>
@@ -8869,24 +7048,12 @@
       <c r="J122" s="5" t="n">
         <v>370.05</v>
       </c>
-      <c r="K122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O122" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P122" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K122" s="5" t="n"/>
+      <c r="L122" s="5" t="n"/>
+      <c r="M122" s="5" t="n"/>
+      <c r="N122" s="5" t="n"/>
+      <c r="O122" s="5" t="n"/>
+      <c r="P122" s="5" t="n"/>
       <c r="Q122" s="5" t="inlineStr">
         <is>
           <t>D0=335.55; 最新=2026-06-03; 相对D0=10.28%</t>
@@ -8938,24 +7105,6 @@
       <c r="J123" t="n">
         <v>215.84</v>
       </c>
-      <c r="K123" t="n">
-        <v/>
-      </c>
-      <c r="L123" t="n">
-        <v/>
-      </c>
-      <c r="M123" t="n">
-        <v/>
-      </c>
-      <c r="N123" t="n">
-        <v/>
-      </c>
-      <c r="O123" t="n">
-        <v/>
-      </c>
-      <c r="P123" t="n">
-        <v/>
-      </c>
       <c r="Q123" t="inlineStr">
         <is>
           <t>D0=211.14; 最新=2026-06-03; 相对D0=2.23%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -9007,24 +7156,12 @@
       <c r="J124" s="5" t="n">
         <v>405.2751</v>
       </c>
-      <c r="K124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O124" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P124" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K124" s="5" t="n"/>
+      <c r="L124" s="5" t="n"/>
+      <c r="M124" s="5" t="n"/>
+      <c r="N124" s="5" t="n"/>
+      <c r="O124" s="5" t="n"/>
+      <c r="P124" s="5" t="n"/>
       <c r="Q124" s="5" t="inlineStr">
         <is>
           <t>D0=374.31; 最新=2026-06-03; 相对D0=8.27%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9076,24 +7213,12 @@
       <c r="J125" s="5" t="n">
         <v>14.22</v>
       </c>
-      <c r="K125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O125" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P125" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K125" s="5" t="n"/>
+      <c r="L125" s="5" t="n"/>
+      <c r="M125" s="5" t="n"/>
+      <c r="N125" s="5" t="n"/>
+      <c r="O125" s="5" t="n"/>
+      <c r="P125" s="5" t="n"/>
       <c r="Q125" s="5" t="inlineStr">
         <is>
           <t>D0=13.77; 最新=2026-06-03; 相对D0=3.27%</t>
@@ -9145,24 +7270,6 @@
       <c r="J126" t="n">
         <v>50.955</v>
       </c>
-      <c r="K126" t="n">
-        <v/>
-      </c>
-      <c r="L126" t="n">
-        <v/>
-      </c>
-      <c r="M126" t="n">
-        <v/>
-      </c>
-      <c r="N126" t="n">
-        <v/>
-      </c>
-      <c r="O126" t="n">
-        <v/>
-      </c>
-      <c r="P126" t="n">
-        <v/>
-      </c>
       <c r="Q126" t="inlineStr">
         <is>
           <t>D0=51.58; 最新=2026-06-03; 相对D0=-1.21%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9214,24 +7321,6 @@
       <c r="J127" t="n">
         <v>181.855</v>
       </c>
-      <c r="K127" t="n">
-        <v/>
-      </c>
-      <c r="L127" t="n">
-        <v/>
-      </c>
-      <c r="M127" t="n">
-        <v/>
-      </c>
-      <c r="N127" t="n">
-        <v/>
-      </c>
-      <c r="O127" t="n">
-        <v/>
-      </c>
-      <c r="P127" t="n">
-        <v/>
-      </c>
       <c r="Q127" t="inlineStr">
         <is>
           <t>D0=185.67; 最新=2026-06-03; 相对D0=-2.05%</t>
@@ -9283,24 +7372,12 @@
       <c r="J128" s="5" t="n">
         <v>14.71</v>
       </c>
-      <c r="K128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O128" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P128" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K128" s="5" t="n"/>
+      <c r="L128" s="5" t="n"/>
+      <c r="M128" s="5" t="n"/>
+      <c r="N128" s="5" t="n"/>
+      <c r="O128" s="5" t="n"/>
+      <c r="P128" s="5" t="n"/>
       <c r="Q128" s="5" t="inlineStr">
         <is>
           <t>D0=14.70; 最新=2026-06-03; 相对D0=0.07%</t>
@@ -9352,24 +7429,12 @@
       <c r="J129" s="5" t="n">
         <v>75.97</v>
       </c>
-      <c r="K129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O129" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P129" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K129" s="5" t="n"/>
+      <c r="L129" s="5" t="n"/>
+      <c r="M129" s="5" t="n"/>
+      <c r="N129" s="5" t="n"/>
+      <c r="O129" s="5" t="n"/>
+      <c r="P129" s="5" t="n"/>
       <c r="Q129" s="5" t="inlineStr">
         <is>
           <t>D0=72.75; 最新=2026-06-03; 相对D0=4.43%</t>
@@ -9421,24 +7486,6 @@
       <c r="J130" t="n">
         <v>314.6</v>
       </c>
-      <c r="K130" t="n">
-        <v/>
-      </c>
-      <c r="L130" t="n">
-        <v/>
-      </c>
-      <c r="M130" t="n">
-        <v/>
-      </c>
-      <c r="N130" t="n">
-        <v/>
-      </c>
-      <c r="O130" t="n">
-        <v/>
-      </c>
-      <c r="P130" t="n">
-        <v/>
-      </c>
       <c r="Q130" t="inlineStr">
         <is>
           <t>D0=320.41; 最新=2026-06-03; 相对D0=-1.81%</t>
@@ -9490,24 +7537,12 @@
       <c r="J131" s="5" t="n">
         <v>190.75</v>
       </c>
-      <c r="K131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O131" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P131" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K131" s="5" t="n"/>
+      <c r="L131" s="5" t="n"/>
+      <c r="M131" s="5" t="n"/>
+      <c r="N131" s="5" t="n"/>
+      <c r="O131" s="5" t="n"/>
+      <c r="P131" s="5" t="n"/>
       <c r="Q131" s="5" t="inlineStr">
         <is>
           <t>D0=185.83; 最新=2026-06-03; 相对D0=2.65%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -9559,24 +7594,12 @@
       <c r="J132" s="5" t="n">
         <v>142.12</v>
       </c>
-      <c r="K132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O132" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P132" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K132" s="5" t="n"/>
+      <c r="L132" s="5" t="n"/>
+      <c r="M132" s="5" t="n"/>
+      <c r="N132" s="5" t="n"/>
+      <c r="O132" s="5" t="n"/>
+      <c r="P132" s="5" t="n"/>
       <c r="Q132" s="5" t="inlineStr">
         <is>
           <t>D0=136.62; 最新=2026-06-03; 相对D0=4.03%</t>
@@ -9628,24 +7651,6 @@
       <c r="J133" t="n">
         <v>8.385</v>
       </c>
-      <c r="K133" t="n">
-        <v/>
-      </c>
-      <c r="L133" t="n">
-        <v/>
-      </c>
-      <c r="M133" t="n">
-        <v/>
-      </c>
-      <c r="N133" t="n">
-        <v/>
-      </c>
-      <c r="O133" t="n">
-        <v/>
-      </c>
-      <c r="P133" t="n">
-        <v/>
-      </c>
       <c r="Q133" t="inlineStr">
         <is>
           <t>D0=8.97; 最新=2026-06-03; 相对D0=-6.52%</t>
@@ -9697,24 +7702,6 @@
       <c r="J134" t="n">
         <v>25.18</v>
       </c>
-      <c r="K134" t="n">
-        <v/>
-      </c>
-      <c r="L134" t="n">
-        <v/>
-      </c>
-      <c r="M134" t="n">
-        <v/>
-      </c>
-      <c r="N134" t="n">
-        <v/>
-      </c>
-      <c r="O134" t="n">
-        <v/>
-      </c>
-      <c r="P134" t="n">
-        <v/>
-      </c>
       <c r="Q134" t="inlineStr">
         <is>
           <t>D0=27.15; 最新=2026-06-03; 相对D0=-7.26%</t>
@@ -9766,24 +7753,6 @@
       <c r="J135" t="n">
         <v>50.38</v>
       </c>
-      <c r="K135" t="n">
-        <v/>
-      </c>
-      <c r="L135" t="n">
-        <v/>
-      </c>
-      <c r="M135" t="n">
-        <v/>
-      </c>
-      <c r="N135" t="n">
-        <v/>
-      </c>
-      <c r="O135" t="n">
-        <v/>
-      </c>
-      <c r="P135" t="n">
-        <v/>
-      </c>
       <c r="Q135" t="inlineStr">
         <is>
           <t>D0=50.55; 最新=2026-06-03; 相对D0=-0.34%</t>
@@ -9835,24 +7804,12 @@
       <c r="J136" s="5" t="n">
         <v>182.975</v>
       </c>
-      <c r="K136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O136" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P136" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K136" s="5" t="n"/>
+      <c r="L136" s="5" t="n"/>
+      <c r="M136" s="5" t="n"/>
+      <c r="N136" s="5" t="n"/>
+      <c r="O136" s="5" t="n"/>
+      <c r="P136" s="5" t="n"/>
       <c r="Q136" s="5" t="inlineStr">
         <is>
           <t>D0=189.00; 最新=2026-06-03; 相对D0=-3.19%</t>
@@ -9904,24 +7861,6 @@
       <c r="J137" t="n">
         <v>938.715</v>
       </c>
-      <c r="K137" t="n">
-        <v/>
-      </c>
-      <c r="L137" t="n">
-        <v/>
-      </c>
-      <c r="M137" t="n">
-        <v/>
-      </c>
-      <c r="N137" t="n">
-        <v/>
-      </c>
-      <c r="O137" t="n">
-        <v/>
-      </c>
-      <c r="P137" t="n">
-        <v/>
-      </c>
       <c r="Q137" t="inlineStr">
         <is>
           <t>D0=905.00; 最新=2026-06-03; 相对D0=3.73%</t>
@@ -9973,24 +7912,6 @@
       <c r="J138" t="n">
         <v>12.27</v>
       </c>
-      <c r="K138" t="n">
-        <v/>
-      </c>
-      <c r="L138" t="n">
-        <v/>
-      </c>
-      <c r="M138" t="n">
-        <v/>
-      </c>
-      <c r="N138" t="n">
-        <v/>
-      </c>
-      <c r="O138" t="n">
-        <v/>
-      </c>
-      <c r="P138" t="n">
-        <v/>
-      </c>
       <c r="Q138" t="inlineStr">
         <is>
           <t>D0=11.02; 最新=2026-06-03; 相对D0=11.34%; 历史重复1次; 重复日期=2026-06-02</t>
@@ -10042,24 +7963,6 @@
       <c r="J139" t="n">
         <v>215.84</v>
       </c>
-      <c r="K139" t="n">
-        <v/>
-      </c>
-      <c r="L139" t="n">
-        <v/>
-      </c>
-      <c r="M139" t="n">
-        <v/>
-      </c>
-      <c r="N139" t="n">
-        <v/>
-      </c>
-      <c r="O139" t="n">
-        <v/>
-      </c>
-      <c r="P139" t="n">
-        <v/>
-      </c>
       <c r="Q139" t="inlineStr">
         <is>
           <t>D0=224.36; 最新=2026-06-03; 相对D0=-3.80%</t>
@@ -10111,24 +8014,12 @@
       <c r="J140" s="5" t="n">
         <v>65.47</v>
       </c>
-      <c r="K140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O140" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P140" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K140" s="5" t="n"/>
+      <c r="L140" s="5" t="n"/>
+      <c r="M140" s="5" t="n"/>
+      <c r="N140" s="5" t="n"/>
+      <c r="O140" s="5" t="n"/>
+      <c r="P140" s="5" t="n"/>
       <c r="Q140" s="5" t="inlineStr">
         <is>
           <t>D0=66.89; 最新=2026-06-03; 相对D0=-2.12%</t>
@@ -10180,24 +8071,12 @@
       <c r="J141" s="5" t="n">
         <v>60.075</v>
       </c>
-      <c r="K141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O141" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P141" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K141" s="5" t="n"/>
+      <c r="L141" s="5" t="n"/>
+      <c r="M141" s="5" t="n"/>
+      <c r="N141" s="5" t="n"/>
+      <c r="O141" s="5" t="n"/>
+      <c r="P141" s="5" t="n"/>
       <c r="Q141" s="5" t="inlineStr">
         <is>
           <t>D0=58.92; 最新=2026-06-03; 相对D0=1.96%</t>
@@ -10249,24 +8128,6 @@
       <c r="J142" t="n">
         <v>14.8749</v>
       </c>
-      <c r="K142" t="n">
-        <v/>
-      </c>
-      <c r="L142" t="n">
-        <v/>
-      </c>
-      <c r="M142" t="n">
-        <v/>
-      </c>
-      <c r="N142" t="n">
-        <v/>
-      </c>
-      <c r="O142" t="n">
-        <v/>
-      </c>
-      <c r="P142" t="n">
-        <v/>
-      </c>
       <c r="Q142" t="inlineStr">
         <is>
           <t>D0=13.89; 最新=2026-06-03; 相对D0=7.09%</t>
@@ -10318,24 +8179,6 @@
       <c r="J143" t="n">
         <v>14.7</v>
       </c>
-      <c r="K143" t="n">
-        <v/>
-      </c>
-      <c r="L143" t="n">
-        <v/>
-      </c>
-      <c r="M143" t="n">
-        <v/>
-      </c>
-      <c r="N143" t="n">
-        <v/>
-      </c>
-      <c r="O143" t="n">
-        <v/>
-      </c>
-      <c r="P143" t="n">
-        <v/>
-      </c>
       <c r="Q143" t="inlineStr">
         <is>
           <t>D0=15.58; 最新=2026-06-03; 相对D0=-5.65%</t>
@@ -10387,24 +8230,12 @@
       <c r="J144" s="5" t="n">
         <v>18.0707</v>
       </c>
-      <c r="K144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O144" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P144" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K144" s="5" t="n"/>
+      <c r="L144" s="5" t="n"/>
+      <c r="M144" s="5" t="n"/>
+      <c r="N144" s="5" t="n"/>
+      <c r="O144" s="5" t="n"/>
+      <c r="P144" s="5" t="n"/>
       <c r="Q144" s="5" t="inlineStr">
         <is>
           <t>D0=17.62; 最新=2026-06-03; 相对D0=2.56%</t>
@@ -10456,24 +8287,6 @@
       <c r="J145" t="n">
         <v>333.79</v>
       </c>
-      <c r="K145" t="n">
-        <v/>
-      </c>
-      <c r="L145" t="n">
-        <v/>
-      </c>
-      <c r="M145" t="n">
-        <v/>
-      </c>
-      <c r="N145" t="n">
-        <v/>
-      </c>
-      <c r="O145" t="n">
-        <v/>
-      </c>
-      <c r="P145" t="n">
-        <v/>
-      </c>
       <c r="Q145" t="inlineStr">
         <is>
           <t>D0=323.39; 最新=2026-06-03; 相对D0=3.22%</t>
@@ -10525,24 +8338,6 @@
       <c r="J146" t="n">
         <v>133.64</v>
       </c>
-      <c r="K146" t="n">
-        <v/>
-      </c>
-      <c r="L146" t="n">
-        <v/>
-      </c>
-      <c r="M146" t="n">
-        <v/>
-      </c>
-      <c r="N146" t="n">
-        <v/>
-      </c>
-      <c r="O146" t="n">
-        <v/>
-      </c>
-      <c r="P146" t="n">
-        <v/>
-      </c>
       <c r="Q146" t="inlineStr">
         <is>
           <t>D0=155.71; 最新=2026-06-03; 相对D0=-14.17%</t>
@@ -10594,24 +8389,6 @@
       <c r="J147" t="n">
         <v>309.355</v>
       </c>
-      <c r="K147" t="n">
-        <v/>
-      </c>
-      <c r="L147" t="n">
-        <v/>
-      </c>
-      <c r="M147" t="n">
-        <v/>
-      </c>
-      <c r="N147" t="n">
-        <v/>
-      </c>
-      <c r="O147" t="n">
-        <v/>
-      </c>
-      <c r="P147" t="n">
-        <v/>
-      </c>
       <c r="Q147" t="inlineStr">
         <is>
           <t>D0=315.20; 最新=2026-06-03; 相对D0=-1.85%</t>
@@ -10663,24 +8440,12 @@
       <c r="J148" s="5" t="n">
         <v>116.43</v>
       </c>
-      <c r="K148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O148" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P148" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K148" s="5" t="n"/>
+      <c r="L148" s="5" t="n"/>
+      <c r="M148" s="5" t="n"/>
+      <c r="N148" s="5" t="n"/>
+      <c r="O148" s="5" t="n"/>
+      <c r="P148" s="5" t="n"/>
       <c r="Q148" s="5" t="inlineStr">
         <is>
           <t>D0=113.00; 最新=2026-06-03; 相对D0=3.04%</t>
@@ -10732,24 +8497,6 @@
       <c r="J149" t="n">
         <v>107.58</v>
       </c>
-      <c r="K149" t="n">
-        <v/>
-      </c>
-      <c r="L149" t="n">
-        <v/>
-      </c>
-      <c r="M149" t="n">
-        <v/>
-      </c>
-      <c r="N149" t="n">
-        <v/>
-      </c>
-      <c r="O149" t="n">
-        <v/>
-      </c>
-      <c r="P149" t="n">
-        <v/>
-      </c>
       <c r="Q149" t="inlineStr">
         <is>
           <t>D0=118.17; 最新=2026-06-03; 相对D0=-8.96%</t>
@@ -10801,24 +8548,6 @@
       <c r="J150" t="n">
         <v>284.4836</v>
       </c>
-      <c r="K150" t="n">
-        <v/>
-      </c>
-      <c r="L150" t="n">
-        <v/>
-      </c>
-      <c r="M150" t="n">
-        <v/>
-      </c>
-      <c r="N150" t="n">
-        <v/>
-      </c>
-      <c r="O150" t="n">
-        <v/>
-      </c>
-      <c r="P150" t="n">
-        <v/>
-      </c>
       <c r="Q150" t="inlineStr">
         <is>
           <t>D0=302.85; 最新=2026-06-03; 相对D0=-6.06%</t>
@@ -10870,24 +8599,12 @@
       <c r="J151" s="5" t="n">
         <v>183.13</v>
       </c>
-      <c r="K151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O151" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P151" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K151" s="5" t="n"/>
+      <c r="L151" s="5" t="n"/>
+      <c r="M151" s="5" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="5" t="n"/>
       <c r="Q151" s="5" t="inlineStr">
         <is>
           <t>D0=187.52; 最新=2026-06-03; 相对D0=-2.34%</t>
@@ -10939,24 +8656,6 @@
       <c r="J152" t="n">
         <v>415.29</v>
       </c>
-      <c r="K152" t="n">
-        <v/>
-      </c>
-      <c r="L152" t="n">
-        <v/>
-      </c>
-      <c r="M152" t="n">
-        <v/>
-      </c>
-      <c r="N152" t="n">
-        <v/>
-      </c>
-      <c r="O152" t="n">
-        <v/>
-      </c>
-      <c r="P152" t="n">
-        <v/>
-      </c>
       <c r="Q152" t="inlineStr">
         <is>
           <t>D0=426.89; 最新=2026-06-03; 相对D0=-2.72%</t>
@@ -11008,24 +8707,12 @@
       <c r="J153" s="5" t="n">
         <v>119.01</v>
       </c>
-      <c r="K153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O153" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P153" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K153" s="5" t="n"/>
+      <c r="L153" s="5" t="n"/>
+      <c r="M153" s="5" t="n"/>
+      <c r="N153" s="5" t="n"/>
+      <c r="O153" s="5" t="n"/>
+      <c r="P153" s="5" t="n"/>
       <c r="Q153" s="5" t="inlineStr">
         <is>
           <t>D0=116.87; 最新=2026-06-03; 相对D0=1.83%</t>
@@ -11077,24 +8764,6 @@
       <c r="J154" t="n">
         <v>209.75</v>
       </c>
-      <c r="K154" t="n">
-        <v/>
-      </c>
-      <c r="L154" t="n">
-        <v/>
-      </c>
-      <c r="M154" t="n">
-        <v/>
-      </c>
-      <c r="N154" t="n">
-        <v/>
-      </c>
-      <c r="O154" t="n">
-        <v/>
-      </c>
-      <c r="P154" t="n">
-        <v/>
-      </c>
       <c r="Q154" t="inlineStr">
         <is>
           <t>D0=229.00; 最新=2026-06-03; 相对D0=-8.41%</t>
@@ -11146,24 +8815,12 @@
       <c r="J155" s="5" t="n">
         <v>190.75</v>
       </c>
-      <c r="K155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O155" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P155" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K155" s="5" t="n"/>
+      <c r="L155" s="5" t="n"/>
+      <c r="M155" s="5" t="n"/>
+      <c r="N155" s="5" t="n"/>
+      <c r="O155" s="5" t="n"/>
+      <c r="P155" s="5" t="n"/>
       <c r="Q155" s="5" t="inlineStr">
         <is>
           <t>D0=187.55; 最新=2026-06-03; 相对D0=1.71%</t>
@@ -11215,24 +8872,6 @@
       <c r="J156" t="n">
         <v>66.3702</v>
       </c>
-      <c r="K156" t="n">
-        <v/>
-      </c>
-      <c r="L156" t="n">
-        <v/>
-      </c>
-      <c r="M156" t="n">
-        <v/>
-      </c>
-      <c r="N156" t="n">
-        <v/>
-      </c>
-      <c r="O156" t="n">
-        <v/>
-      </c>
-      <c r="P156" t="n">
-        <v/>
-      </c>
       <c r="Q156" t="inlineStr">
         <is>
           <t>D0=66.47; 最新=2026-06-03; 相对D0=-0.15%</t>
@@ -11284,24 +8923,12 @@
       <c r="J157" s="5" t="n">
         <v>48.21</v>
       </c>
-      <c r="K157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O157" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P157" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K157" s="5" t="n"/>
+      <c r="L157" s="5" t="n"/>
+      <c r="M157" s="5" t="n"/>
+      <c r="N157" s="5" t="n"/>
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="5" t="n"/>
       <c r="Q157" s="5" t="inlineStr">
         <is>
           <t>D0=48.66; 最新=2026-06-03; 相对D0=-0.92%</t>
@@ -11353,24 +8980,6 @@
       <c r="J158" t="n">
         <v>67.94</v>
       </c>
-      <c r="K158" t="n">
-        <v/>
-      </c>
-      <c r="L158" t="n">
-        <v/>
-      </c>
-      <c r="M158" t="n">
-        <v/>
-      </c>
-      <c r="N158" t="n">
-        <v/>
-      </c>
-      <c r="O158" t="n">
-        <v/>
-      </c>
-      <c r="P158" t="n">
-        <v/>
-      </c>
       <c r="Q158" t="inlineStr">
         <is>
           <t>D0=72.33; 最新=2026-06-03; 相对D0=-6.07%</t>
@@ -11422,24 +9031,12 @@
       <c r="J159" s="5" t="n">
         <v>140.75</v>
       </c>
-      <c r="K159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O159" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P159" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K159" s="5" t="n"/>
+      <c r="L159" s="5" t="n"/>
+      <c r="M159" s="5" t="n"/>
+      <c r="N159" s="5" t="n"/>
+      <c r="O159" s="5" t="n"/>
+      <c r="P159" s="5" t="n"/>
       <c r="Q159" s="5" t="inlineStr">
         <is>
           <t>D0=142.92; 最新=2026-06-03; 相对D0=-1.52%</t>
@@ -11491,24 +9088,12 @@
       <c r="J160" s="5" t="n">
         <v>142.12</v>
       </c>
-      <c r="K160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O160" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P160" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K160" s="5" t="n"/>
+      <c r="L160" s="5" t="n"/>
+      <c r="M160" s="5" t="n"/>
+      <c r="N160" s="5" t="n"/>
+      <c r="O160" s="5" t="n"/>
+      <c r="P160" s="5" t="n"/>
       <c r="Q160" s="5" t="inlineStr">
         <is>
           <t>D0=138.58; 最新=2026-06-03; 相对D0=2.55%</t>
@@ -11560,24 +9145,12 @@
       <c r="J161" s="5" t="n">
         <v>419.695</v>
       </c>
-      <c r="K161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O161" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P161" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K161" s="5" t="n"/>
+      <c r="L161" s="5" t="n"/>
+      <c r="M161" s="5" t="n"/>
+      <c r="N161" s="5" t="n"/>
+      <c r="O161" s="5" t="n"/>
+      <c r="P161" s="5" t="n"/>
       <c r="Q161" s="5" t="inlineStr">
         <is>
           <t>D0=417.62; 最新=2026-06-03; 相对D0=0.50%</t>
@@ -11629,24 +9202,6 @@
       <c r="J162" t="n">
         <v>199.5</v>
       </c>
-      <c r="K162" t="n">
-        <v/>
-      </c>
-      <c r="L162" t="n">
-        <v/>
-      </c>
-      <c r="M162" t="n">
-        <v/>
-      </c>
-      <c r="N162" t="n">
-        <v/>
-      </c>
-      <c r="O162" t="n">
-        <v/>
-      </c>
-      <c r="P162" t="n">
-        <v/>
-      </c>
       <c r="Q162" t="inlineStr">
         <is>
           <t>D0=200.40; 最新=2026-06-03; 相对D0=-0.45%</t>
@@ -11698,24 +9253,6 @@
       <c r="J163" t="n">
         <v>12.27</v>
       </c>
-      <c r="K163" t="n">
-        <v/>
-      </c>
-      <c r="L163" t="n">
-        <v/>
-      </c>
-      <c r="M163" t="n">
-        <v/>
-      </c>
-      <c r="N163" t="n">
-        <v/>
-      </c>
-      <c r="O163" t="n">
-        <v/>
-      </c>
-      <c r="P163" t="n">
-        <v/>
-      </c>
       <c r="Q163" t="inlineStr">
         <is>
           <t>D0=12.72; 最新=2026-06-03; 相对D0=-3.54%</t>
@@ -11767,24 +9304,6 @@
       <c r="J164" t="n">
         <v>11.1214</v>
       </c>
-      <c r="K164" t="n">
-        <v/>
-      </c>
-      <c r="L164" t="n">
-        <v/>
-      </c>
-      <c r="M164" t="n">
-        <v/>
-      </c>
-      <c r="N164" t="n">
-        <v/>
-      </c>
-      <c r="O164" t="n">
-        <v/>
-      </c>
-      <c r="P164" t="n">
-        <v/>
-      </c>
       <c r="Q164" t="inlineStr">
         <is>
           <t>D0=11.72; 最新=2026-06-03; 相对D0=-5.11%</t>
@@ -11836,24 +9355,6 @@
       <c r="J165" t="n">
         <v>23.435</v>
       </c>
-      <c r="K165" t="n">
-        <v/>
-      </c>
-      <c r="L165" t="n">
-        <v/>
-      </c>
-      <c r="M165" t="n">
-        <v/>
-      </c>
-      <c r="N165" t="n">
-        <v/>
-      </c>
-      <c r="O165" t="n">
-        <v/>
-      </c>
-      <c r="P165" t="n">
-        <v/>
-      </c>
       <c r="Q165" t="inlineStr">
         <is>
           <t>D0=23.30; 最新=2026-06-03; 相对D0=0.58%</t>
@@ -11905,24 +9406,12 @@
       <c r="J166" s="5" t="n">
         <v>131.92</v>
       </c>
-      <c r="K166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O166" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P166" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K166" s="5" t="n"/>
+      <c r="L166" s="5" t="n"/>
+      <c r="M166" s="5" t="n"/>
+      <c r="N166" s="5" t="n"/>
+      <c r="O166" s="5" t="n"/>
+      <c r="P166" s="5" t="n"/>
       <c r="Q166" s="5" t="inlineStr">
         <is>
           <t>D0=138.17; 最新=2026-06-03; 相对D0=-4.52%</t>
@@ -11974,24 +9463,12 @@
       <c r="J167" s="5" t="n">
         <v>133.145</v>
       </c>
-      <c r="K167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O167" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P167" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K167" s="5" t="n"/>
+      <c r="L167" s="5" t="n"/>
+      <c r="M167" s="5" t="n"/>
+      <c r="N167" s="5" t="n"/>
+      <c r="O167" s="5" t="n"/>
+      <c r="P167" s="5" t="n"/>
       <c r="Q167" s="5" t="inlineStr">
         <is>
           <t>D0=133.51; 最新=2026-06-03; 相对D0=-0.27%</t>
@@ -12043,24 +9520,12 @@
       <c r="J168" s="5" t="n">
         <v>65.47</v>
       </c>
-      <c r="K168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O168" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P168" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K168" s="5" t="n"/>
+      <c r="L168" s="5" t="n"/>
+      <c r="M168" s="5" t="n"/>
+      <c r="N168" s="5" t="n"/>
+      <c r="O168" s="5" t="n"/>
+      <c r="P168" s="5" t="n"/>
       <c r="Q168" s="5" t="inlineStr">
         <is>
           <t>D0=73.47; 最新=2026-06-03; 相对D0=-10.89%</t>
@@ -12112,24 +9577,12 @@
       <c r="J169" s="5" t="n">
         <v>276.67</v>
       </c>
-      <c r="K169" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L169" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M169" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N169" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O169" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P169" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K169" s="5" t="n"/>
+      <c r="L169" s="5" t="n"/>
+      <c r="M169" s="5" t="n"/>
+      <c r="N169" s="5" t="n"/>
+      <c r="O169" s="5" t="n"/>
+      <c r="P169" s="5" t="n"/>
       <c r="Q169" s="5" t="inlineStr">
         <is>
           <t>D0=278.02; 最新=2026-06-03; 相对D0=-0.49%</t>
@@ -12181,24 +9634,6 @@
       <c r="J170" t="n">
         <v>57.25</v>
       </c>
-      <c r="K170" t="n">
-        <v/>
-      </c>
-      <c r="L170" t="n">
-        <v/>
-      </c>
-      <c r="M170" t="n">
-        <v/>
-      </c>
-      <c r="N170" t="n">
-        <v/>
-      </c>
-      <c r="O170" t="n">
-        <v/>
-      </c>
-      <c r="P170" t="n">
-        <v/>
-      </c>
       <c r="Q170" t="inlineStr">
         <is>
           <t>D0=56.89; 最新=2026-06-03; 相对D0=0.63%</t>
@@ -12250,24 +9685,12 @@
       <c r="J171" s="5" t="n">
         <v>56.78</v>
       </c>
-      <c r="K171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O171" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P171" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K171" s="5" t="n"/>
+      <c r="L171" s="5" t="n"/>
+      <c r="M171" s="5" t="n"/>
+      <c r="N171" s="5" t="n"/>
+      <c r="O171" s="5" t="n"/>
+      <c r="P171" s="5" t="n"/>
       <c r="Q171" s="5" t="inlineStr">
         <is>
           <t>D0=56.56; 最新=2026-06-03; 相对D0=0.39%</t>
@@ -12319,24 +9742,6 @@
       <c r="J172" t="n">
         <v>496.49</v>
       </c>
-      <c r="K172" t="n">
-        <v/>
-      </c>
-      <c r="L172" t="n">
-        <v/>
-      </c>
-      <c r="M172" t="n">
-        <v/>
-      </c>
-      <c r="N172" t="n">
-        <v/>
-      </c>
-      <c r="O172" t="n">
-        <v/>
-      </c>
-      <c r="P172" t="n">
-        <v/>
-      </c>
       <c r="Q172" t="inlineStr">
         <is>
           <t>D0=508.35; 最新=2026-06-03; 相对D0=-2.33%</t>
@@ -12388,24 +9793,6 @@
       <c r="J173" t="n">
         <v>87.59999999999999</v>
       </c>
-      <c r="K173" t="n">
-        <v/>
-      </c>
-      <c r="L173" t="n">
-        <v/>
-      </c>
-      <c r="M173" t="n">
-        <v/>
-      </c>
-      <c r="N173" t="n">
-        <v/>
-      </c>
-      <c r="O173" t="n">
-        <v/>
-      </c>
-      <c r="P173" t="n">
-        <v/>
-      </c>
       <c r="Q173" t="inlineStr">
         <is>
           <t>D0=87.39; 最新=2026-06-03; 相对D0=0.24%</t>
@@ -12457,24 +9844,12 @@
       <c r="J174" s="5" t="n">
         <v>405.2751</v>
       </c>
-      <c r="K174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O174" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P174" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K174" s="5" t="n"/>
+      <c r="L174" s="5" t="n"/>
+      <c r="M174" s="5" t="n"/>
+      <c r="N174" s="5" t="n"/>
+      <c r="O174" s="5" t="n"/>
+      <c r="P174" s="5" t="n"/>
       <c r="Q174" s="5" t="inlineStr">
         <is>
           <t>D0=392.62; 最新=2026-06-03; 相对D0=3.22%</t>
@@ -12526,24 +9901,12 @@
       <c r="J175" s="5" t="n">
         <v>377.915</v>
       </c>
-      <c r="K175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O175" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P175" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K175" s="5" t="n"/>
+      <c r="L175" s="5" t="n"/>
+      <c r="M175" s="5" t="n"/>
+      <c r="N175" s="5" t="n"/>
+      <c r="O175" s="5" t="n"/>
+      <c r="P175" s="5" t="n"/>
       <c r="Q175" s="5" t="inlineStr">
         <is>
           <t>D0=385.51; 最新=2026-06-03; 相对D0=-1.97%</t>
@@ -12595,24 +9958,12 @@
       <c r="J176" s="5" t="n">
         <v>14.22</v>
       </c>
-      <c r="K176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O176" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P176" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K176" s="5" t="n"/>
+      <c r="L176" s="5" t="n"/>
+      <c r="M176" s="5" t="n"/>
+      <c r="N176" s="5" t="n"/>
+      <c r="O176" s="5" t="n"/>
+      <c r="P176" s="5" t="n"/>
       <c r="Q176" s="5" t="inlineStr">
         <is>
           <t>D0=15.44; 最新=2026-06-03; 相对D0=-7.90%</t>
@@ -12664,24 +10015,12 @@
       <c r="J177" s="5" t="n">
         <v>18.0707</v>
       </c>
-      <c r="K177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O177" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P177" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K177" s="5" t="n"/>
+      <c r="L177" s="5" t="n"/>
+      <c r="M177" s="5" t="n"/>
+      <c r="N177" s="5" t="n"/>
+      <c r="O177" s="5" t="n"/>
+      <c r="P177" s="5" t="n"/>
       <c r="Q177" s="5" t="inlineStr">
         <is>
           <t>D0=19.54; 最新=2026-06-03; 相对D0=-7.52%</t>
@@ -12733,24 +10072,6 @@
       <c r="J178" t="n">
         <v>333.79</v>
       </c>
-      <c r="K178" t="n">
-        <v/>
-      </c>
-      <c r="L178" t="n">
-        <v/>
-      </c>
-      <c r="M178" t="n">
-        <v/>
-      </c>
-      <c r="N178" t="n">
-        <v/>
-      </c>
-      <c r="O178" t="n">
-        <v/>
-      </c>
-      <c r="P178" t="n">
-        <v/>
-      </c>
       <c r="Q178" t="inlineStr">
         <is>
           <t>D0=334.49; 最新=2026-06-03; 相对D0=-0.21%</t>
@@ -12802,24 +10123,12 @@
       <c r="J179" s="5" t="n">
         <v>153.41</v>
       </c>
-      <c r="K179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O179" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P179" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K179" s="5" t="n"/>
+      <c r="L179" s="5" t="n"/>
+      <c r="M179" s="5" t="n"/>
+      <c r="N179" s="5" t="n"/>
+      <c r="O179" s="5" t="n"/>
+      <c r="P179" s="5" t="n"/>
       <c r="Q179" s="5" t="inlineStr">
         <is>
           <t>D0=157.97; 最新=2026-06-03; 相对D0=-2.89%</t>
@@ -12871,24 +10180,6 @@
       <c r="J180" t="n">
         <v>51.675</v>
       </c>
-      <c r="K180" t="n">
-        <v/>
-      </c>
-      <c r="L180" t="n">
-        <v/>
-      </c>
-      <c r="M180" t="n">
-        <v/>
-      </c>
-      <c r="N180" t="n">
-        <v/>
-      </c>
-      <c r="O180" t="n">
-        <v/>
-      </c>
-      <c r="P180" t="n">
-        <v/>
-      </c>
       <c r="Q180" t="inlineStr">
         <is>
           <t>D0=51.52; 最新=2026-06-03; 相对D0=0.30%</t>
@@ -12940,24 +10231,12 @@
       <c r="J181" s="5" t="n">
         <v>59.085</v>
       </c>
-      <c r="K181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O181" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P181" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K181" s="5" t="n"/>
+      <c r="L181" s="5" t="n"/>
+      <c r="M181" s="5" t="n"/>
+      <c r="N181" s="5" t="n"/>
+      <c r="O181" s="5" t="n"/>
+      <c r="P181" s="5" t="n"/>
       <c r="Q181" s="5" t="inlineStr">
         <is>
           <t>D0=57.96; 最新=2026-06-03; 相对D0=1.94%</t>
@@ -13009,24 +10288,6 @@
       <c r="J182" t="n">
         <v>50.955</v>
       </c>
-      <c r="K182" t="n">
-        <v/>
-      </c>
-      <c r="L182" t="n">
-        <v/>
-      </c>
-      <c r="M182" t="n">
-        <v/>
-      </c>
-      <c r="N182" t="n">
-        <v/>
-      </c>
-      <c r="O182" t="n">
-        <v/>
-      </c>
-      <c r="P182" t="n">
-        <v/>
-      </c>
       <c r="Q182" t="inlineStr">
         <is>
           <t>D0=51.46; 最新=2026-06-03; 相对D0=-0.98%</t>
@@ -13078,24 +10339,12 @@
       <c r="J183" s="5" t="n">
         <v>44.125</v>
       </c>
-      <c r="K183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O183" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P183" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K183" s="5" t="n"/>
+      <c r="L183" s="5" t="n"/>
+      <c r="M183" s="5" t="n"/>
+      <c r="N183" s="5" t="n"/>
+      <c r="O183" s="5" t="n"/>
+      <c r="P183" s="5" t="n"/>
       <c r="Q183" s="5" t="inlineStr">
         <is>
           <t>D0=44.12; 最新=2026-06-03; 相对D0=0.00%</t>
@@ -13332,24 +10581,6 @@
       <c r="J195" t="n">
         <v>45.88</v>
       </c>
-      <c r="K195" t="n">
-        <v/>
-      </c>
-      <c r="L195" t="n">
-        <v/>
-      </c>
-      <c r="M195" t="n">
-        <v/>
-      </c>
-      <c r="N195" t="n">
-        <v/>
-      </c>
-      <c r="O195" t="n">
-        <v/>
-      </c>
-      <c r="P195" t="n">
-        <v/>
-      </c>
       <c r="Q195" t="inlineStr">
         <is>
           <t>D0=45.88; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13401,24 +10632,6 @@
       <c r="J196" t="n">
         <v>16.315</v>
       </c>
-      <c r="K196" t="n">
-        <v/>
-      </c>
-      <c r="L196" t="n">
-        <v/>
-      </c>
-      <c r="M196" t="n">
-        <v/>
-      </c>
-      <c r="N196" t="n">
-        <v/>
-      </c>
-      <c r="O196" t="n">
-        <v/>
-      </c>
-      <c r="P196" t="n">
-        <v/>
-      </c>
       <c r="Q196" t="inlineStr">
         <is>
           <t>D0=16.32; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13470,24 +10683,12 @@
       <c r="J197" s="5" t="n">
         <v>209.81</v>
       </c>
-      <c r="K197" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L197" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M197" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N197" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O197" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P197" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K197" s="5" t="n"/>
+      <c r="L197" s="5" t="n"/>
+      <c r="M197" s="5" t="n"/>
+      <c r="N197" s="5" t="n"/>
+      <c r="O197" s="5" t="n"/>
+      <c r="P197" s="5" t="n"/>
       <c r="Q197" s="5" t="inlineStr">
         <is>
           <t>D0=209.81; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -13539,24 +10740,6 @@
       <c r="J198" t="n">
         <v>112</v>
       </c>
-      <c r="K198" t="n">
-        <v/>
-      </c>
-      <c r="L198" t="n">
-        <v/>
-      </c>
-      <c r="M198" t="n">
-        <v/>
-      </c>
-      <c r="N198" t="n">
-        <v/>
-      </c>
-      <c r="O198" t="n">
-        <v/>
-      </c>
-      <c r="P198" t="n">
-        <v/>
-      </c>
       <c r="Q198" t="inlineStr">
         <is>
           <t>D0=112.00; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13608,24 +10791,6 @@
       <c r="J199" t="n">
         <v>8.385</v>
       </c>
-      <c r="K199" t="n">
-        <v/>
-      </c>
-      <c r="L199" t="n">
-        <v/>
-      </c>
-      <c r="M199" t="n">
-        <v/>
-      </c>
-      <c r="N199" t="n">
-        <v/>
-      </c>
-      <c r="O199" t="n">
-        <v/>
-      </c>
-      <c r="P199" t="n">
-        <v/>
-      </c>
       <c r="Q199" t="inlineStr">
         <is>
           <t>D0=8.38; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13677,24 +10842,6 @@
       <c r="J200" t="n">
         <v>83.62</v>
       </c>
-      <c r="K200" t="n">
-        <v/>
-      </c>
-      <c r="L200" t="n">
-        <v/>
-      </c>
-      <c r="M200" t="n">
-        <v/>
-      </c>
-      <c r="N200" t="n">
-        <v/>
-      </c>
-      <c r="O200" t="n">
-        <v/>
-      </c>
-      <c r="P200" t="n">
-        <v/>
-      </c>
       <c r="Q200" t="inlineStr">
         <is>
           <t>D0=83.62; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(预警卖出)</t>
@@ -13746,24 +10893,6 @@
       <c r="J201" t="n">
         <v>425.555</v>
       </c>
-      <c r="K201" t="n">
-        <v/>
-      </c>
-      <c r="L201" t="n">
-        <v/>
-      </c>
-      <c r="M201" t="n">
-        <v/>
-      </c>
-      <c r="N201" t="n">
-        <v/>
-      </c>
-      <c r="O201" t="n">
-        <v/>
-      </c>
-      <c r="P201" t="n">
-        <v/>
-      </c>
       <c r="Q201" t="inlineStr">
         <is>
           <t>D0=425.56; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13815,24 +10944,12 @@
       <c r="J202" s="5" t="n">
         <v>25.89</v>
       </c>
-      <c r="K202" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L202" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M202" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N202" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O202" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P202" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K202" s="5" t="n"/>
+      <c r="L202" s="5" t="n"/>
+      <c r="M202" s="5" t="n"/>
+      <c r="N202" s="5" t="n"/>
+      <c r="O202" s="5" t="n"/>
+      <c r="P202" s="5" t="n"/>
       <c r="Q202" s="5" t="inlineStr">
         <is>
           <t>D0=25.89; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -13884,24 +11001,12 @@
       <c r="J203" s="5" t="n">
         <v>65.48</v>
       </c>
-      <c r="K203" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L203" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M203" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N203" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O203" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P203" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K203" s="5" t="n"/>
+      <c r="L203" s="5" t="n"/>
+      <c r="M203" s="5" t="n"/>
+      <c r="N203" s="5" t="n"/>
+      <c r="O203" s="5" t="n"/>
+      <c r="P203" s="5" t="n"/>
       <c r="Q203" s="5" t="inlineStr">
         <is>
           <t>D0=65.48; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -13953,24 +11058,6 @@
       <c r="J204" t="n">
         <v>142.81</v>
       </c>
-      <c r="K204" t="n">
-        <v/>
-      </c>
-      <c r="L204" t="n">
-        <v/>
-      </c>
-      <c r="M204" t="n">
-        <v/>
-      </c>
-      <c r="N204" t="n">
-        <v/>
-      </c>
-      <c r="O204" t="n">
-        <v/>
-      </c>
-      <c r="P204" t="n">
-        <v/>
-      </c>
       <c r="Q204" t="inlineStr">
         <is>
           <t>D0=142.81; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14022,24 +11109,6 @@
       <c r="J205" t="n">
         <v>14.7064</v>
       </c>
-      <c r="K205" t="n">
-        <v/>
-      </c>
-      <c r="L205" t="n">
-        <v/>
-      </c>
-      <c r="M205" t="n">
-        <v/>
-      </c>
-      <c r="N205" t="n">
-        <v/>
-      </c>
-      <c r="O205" t="n">
-        <v/>
-      </c>
-      <c r="P205" t="n">
-        <v/>
-      </c>
       <c r="Q205" t="inlineStr">
         <is>
           <t>D0=14.71; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -14091,24 +11160,12 @@
       <c r="J206" s="5" t="n">
         <v>12.2</v>
       </c>
-      <c r="K206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O206" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P206" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="5" t="n"/>
+      <c r="M206" s="5" t="n"/>
+      <c r="N206" s="5" t="n"/>
+      <c r="O206" s="5" t="n"/>
+      <c r="P206" s="5" t="n"/>
       <c r="Q206" s="5" t="inlineStr">
         <is>
           <t>D0=12.20; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14160,24 +11217,6 @@
       <c r="J207" t="n">
         <v>16.7099</v>
       </c>
-      <c r="K207" t="n">
-        <v/>
-      </c>
-      <c r="L207" t="n">
-        <v/>
-      </c>
-      <c r="M207" t="n">
-        <v/>
-      </c>
-      <c r="N207" t="n">
-        <v/>
-      </c>
-      <c r="O207" t="n">
-        <v/>
-      </c>
-      <c r="P207" t="n">
-        <v/>
-      </c>
       <c r="Q207" t="inlineStr">
         <is>
           <t>D0=16.71; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出 | 预警卖出)</t>
@@ -14229,24 +11268,12 @@
       <c r="J208" s="5" t="n">
         <v>153.41</v>
       </c>
-      <c r="K208" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L208" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M208" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N208" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O208" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P208" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K208" s="5" t="n"/>
+      <c r="L208" s="5" t="n"/>
+      <c r="M208" s="5" t="n"/>
+      <c r="N208" s="5" t="n"/>
+      <c r="O208" s="5" t="n"/>
+      <c r="P208" s="5" t="n"/>
       <c r="Q208" s="5" t="inlineStr">
         <is>
           <t>D0=153.41; 最新=2026-06-03; 相对D0=0.00%; 本次触发=2026-06-03(正式卖出)</t>
@@ -14298,24 +11325,12 @@
       <c r="J209" s="5" t="n">
         <v>40.92</v>
       </c>
-      <c r="K209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O209" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P209" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K209" s="5" t="n"/>
+      <c r="L209" s="5" t="n"/>
+      <c r="M209" s="5" t="n"/>
+      <c r="N209" s="5" t="n"/>
+      <c r="O209" s="5" t="n"/>
+      <c r="P209" s="5" t="n"/>
       <c r="Q209" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-06-03; 相对D0=-1.33%</t>
@@ -14336,7 +11351,6 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="D210" t="inlineStr"/>
       <c r="E210" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -14363,24 +11377,6 @@
       <c r="J210" t="n">
         <v>91.02</v>
       </c>
-      <c r="K210" t="n">
-        <v/>
-      </c>
-      <c r="L210" t="n">
-        <v/>
-      </c>
-      <c r="M210" t="n">
-        <v/>
-      </c>
-      <c r="N210" t="n">
-        <v/>
-      </c>
-      <c r="O210" t="n">
-        <v/>
-      </c>
-      <c r="P210" t="n">
-        <v/>
-      </c>
       <c r="Q210" t="inlineStr">
         <is>
           <t>D0=90.64; 最新=2026-06-03; 相对D0=0.42%</t>
@@ -14432,24 +11428,12 @@
       <c r="J211" s="5" t="n">
         <v>190.755</v>
       </c>
-      <c r="K211" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L211" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M211" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N211" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O211" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P211" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K211" s="5" t="n"/>
+      <c r="L211" s="5" t="n"/>
+      <c r="M211" s="5" t="n"/>
+      <c r="N211" s="5" t="n"/>
+      <c r="O211" s="5" t="n"/>
+      <c r="P211" s="5" t="n"/>
       <c r="Q211" s="5" t="inlineStr">
         <is>
           <t>D0=184.71; 最新=2026-06-03; 相对D0=3.27%</t>
@@ -14501,24 +11485,12 @@
       <c r="J212" s="5" t="n">
         <v>142.12</v>
       </c>
-      <c r="K212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O212" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P212" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K212" s="5" t="n"/>
+      <c r="L212" s="5" t="n"/>
+      <c r="M212" s="5" t="n"/>
+      <c r="N212" s="5" t="n"/>
+      <c r="O212" s="5" t="n"/>
+      <c r="P212" s="5" t="n"/>
       <c r="Q212" s="5" t="inlineStr">
         <is>
           <t>D0=136.20; 最新=2026-06-03; 相对D0=4.35%</t>
@@ -14570,24 +11542,6 @@
       <c r="J213" t="n">
         <v>370.62</v>
       </c>
-      <c r="K213" t="n">
-        <v/>
-      </c>
-      <c r="L213" t="n">
-        <v/>
-      </c>
-      <c r="M213" t="n">
-        <v/>
-      </c>
-      <c r="N213" t="n">
-        <v/>
-      </c>
-      <c r="O213" t="n">
-        <v/>
-      </c>
-      <c r="P213" t="n">
-        <v/>
-      </c>
       <c r="Q213" t="inlineStr">
         <is>
           <t>D0=307.35; 最新=2026-06-03; 相对D0=20.59%</t>
@@ -14639,24 +11593,12 @@
       <c r="J214" s="5" t="n">
         <v>60.075</v>
       </c>
-      <c r="K214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O214" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P214" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K214" s="5" t="n"/>
+      <c r="L214" s="5" t="n"/>
+      <c r="M214" s="5" t="n"/>
+      <c r="N214" s="5" t="n"/>
+      <c r="O214" s="5" t="n"/>
+      <c r="P214" s="5" t="n"/>
       <c r="Q214" s="5" t="inlineStr">
         <is>
           <t>D0=57.46; 最新=2026-06-03; 相对D0=4.55%</t>
@@ -14708,24 +11650,12 @@
       <c r="J215" s="5" t="n">
         <v>14.885</v>
       </c>
-      <c r="K215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O215" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P215" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K215" s="5" t="n"/>
+      <c r="L215" s="5" t="n"/>
+      <c r="M215" s="5" t="n"/>
+      <c r="N215" s="5" t="n"/>
+      <c r="O215" s="5" t="n"/>
+      <c r="P215" s="5" t="n"/>
       <c r="Q215" s="5" t="inlineStr">
         <is>
           <t>D0=13.35; 最新=2026-06-03; 相对D0=11.50%</t>
@@ -14777,24 +11707,12 @@
       <c r="J216" s="5" t="n">
         <v>59.085</v>
       </c>
-      <c r="K216" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L216" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M216" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N216" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O216" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P216" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K216" s="5" t="n"/>
+      <c r="L216" s="5" t="n"/>
+      <c r="M216" s="5" t="n"/>
+      <c r="N216" s="5" t="n"/>
+      <c r="O216" s="5" t="n"/>
+      <c r="P216" s="5" t="n"/>
       <c r="Q216" s="5" t="inlineStr">
         <is>
           <t>D0=57.85; 最新=2026-06-03; 相对D0=2.13%</t>
@@ -14846,24 +11764,12 @@
       <c r="J217" s="5" t="n">
         <v>56.75</v>
       </c>
-      <c r="K217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O217" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P217" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K217" s="5" t="n"/>
+      <c r="L217" s="5" t="n"/>
+      <c r="M217" s="5" t="n"/>
+      <c r="N217" s="5" t="n"/>
+      <c r="O217" s="5" t="n"/>
+      <c r="P217" s="5" t="n"/>
       <c r="Q217" s="5" t="inlineStr">
         <is>
           <t>D0=56.50; 最新=2026-06-03; 相对D0=0.44%</t>
@@ -14915,24 +11821,6 @@
       <c r="J218" t="n">
         <v>133.63</v>
       </c>
-      <c r="K218" t="n">
-        <v/>
-      </c>
-      <c r="L218" t="n">
-        <v/>
-      </c>
-      <c r="M218" t="n">
-        <v/>
-      </c>
-      <c r="N218" t="n">
-        <v/>
-      </c>
-      <c r="O218" t="n">
-        <v/>
-      </c>
-      <c r="P218" t="n">
-        <v/>
-      </c>
       <c r="Q218" t="inlineStr">
         <is>
           <t>D0=126.41; 最新=2026-06-03; 相对D0=5.71%</t>
@@ -14984,24 +11872,12 @@
       <c r="J219" s="5" t="n">
         <v>106.56</v>
       </c>
-      <c r="K219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O219" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P219" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K219" s="5" t="n"/>
+      <c r="L219" s="5" t="n"/>
+      <c r="M219" s="5" t="n"/>
+      <c r="N219" s="5" t="n"/>
+      <c r="O219" s="5" t="n"/>
+      <c r="P219" s="5" t="n"/>
       <c r="Q219" s="5" t="inlineStr">
         <is>
           <t>D0=115.70; 最新=2026-06-03; 相对D0=-7.90%</t>
@@ -15053,24 +11929,12 @@
       <c r="J220" s="5" t="n">
         <v>266.28</v>
       </c>
-      <c r="K220" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L220" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M220" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N220" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O220" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P220" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K220" s="5" t="n"/>
+      <c r="L220" s="5" t="n"/>
+      <c r="M220" s="5" t="n"/>
+      <c r="N220" s="5" t="n"/>
+      <c r="O220" s="5" t="n"/>
+      <c r="P220" s="5" t="n"/>
       <c r="Q220" s="5" t="inlineStr">
         <is>
           <t>D0=286.31; 最新=2026-06-03; 相对D0=-7.00%</t>
@@ -15122,24 +11986,12 @@
       <c r="J221" s="5" t="n">
         <v>199.53</v>
       </c>
-      <c r="K221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O221" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P221" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K221" s="5" t="n"/>
+      <c r="L221" s="5" t="n"/>
+      <c r="M221" s="5" t="n"/>
+      <c r="N221" s="5" t="n"/>
+      <c r="O221" s="5" t="n"/>
+      <c r="P221" s="5" t="n"/>
       <c r="Q221" s="5" t="inlineStr">
         <is>
           <t>D0=182.97; 最新=2026-06-03; 相对D0=9.05%</t>
@@ -15191,24 +12043,6 @@
       <c r="J222" t="n">
         <v>496.49</v>
       </c>
-      <c r="K222" t="n">
-        <v/>
-      </c>
-      <c r="L222" t="n">
-        <v/>
-      </c>
-      <c r="M222" t="n">
-        <v/>
-      </c>
-      <c r="N222" t="n">
-        <v/>
-      </c>
-      <c r="O222" t="n">
-        <v/>
-      </c>
-      <c r="P222" t="n">
-        <v/>
-      </c>
       <c r="Q222" t="inlineStr">
         <is>
           <t>D0=480.64; 最新=2026-06-03; 相对D0=3.30%</t>
@@ -15260,24 +12094,12 @@
       <c r="J223" s="5" t="n">
         <v>116.43</v>
       </c>
-      <c r="K223" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L223" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M223" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N223" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O223" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P223" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K223" s="5" t="n"/>
+      <c r="L223" s="5" t="n"/>
+      <c r="M223" s="5" t="n"/>
+      <c r="N223" s="5" t="n"/>
+      <c r="O223" s="5" t="n"/>
+      <c r="P223" s="5" t="n"/>
       <c r="Q223" s="5" t="inlineStr">
         <is>
           <t>D0=92.33; 最新=2026-06-03; 相对D0=26.10%</t>
@@ -15329,24 +12151,12 @@
       <c r="J224" s="5" t="n">
         <v>76.02</v>
       </c>
-      <c r="K224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O224" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P224" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K224" s="5" t="n"/>
+      <c r="L224" s="5" t="n"/>
+      <c r="M224" s="5" t="n"/>
+      <c r="N224" s="5" t="n"/>
+      <c r="O224" s="5" t="n"/>
+      <c r="P224" s="5" t="n"/>
       <c r="Q224" s="5" t="inlineStr">
         <is>
           <t>D0=69.56; 最新=2026-06-03; 相对D0=9.29%</t>
@@ -15398,24 +12208,6 @@
       <c r="J225" t="n">
         <v>284.67</v>
       </c>
-      <c r="K225" t="n">
-        <v/>
-      </c>
-      <c r="L225" t="n">
-        <v/>
-      </c>
-      <c r="M225" t="n">
-        <v/>
-      </c>
-      <c r="N225" t="n">
-        <v/>
-      </c>
-      <c r="O225" t="n">
-        <v/>
-      </c>
-      <c r="P225" t="n">
-        <v/>
-      </c>
       <c r="Q225" t="inlineStr">
         <is>
           <t>D0=285.00; 最新=2026-06-03; 相对D0=-0.12%</t>
@@ -15467,24 +12259,12 @@
       <c r="J226" s="5" t="n">
         <v>183.105</v>
       </c>
-      <c r="K226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O226" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P226" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K226" s="5" t="n"/>
+      <c r="L226" s="5" t="n"/>
+      <c r="M226" s="5" t="n"/>
+      <c r="N226" s="5" t="n"/>
+      <c r="O226" s="5" t="n"/>
+      <c r="P226" s="5" t="n"/>
       <c r="Q226" s="5" t="inlineStr">
         <is>
           <t>D0=171.66; 最新=2026-06-03; 相对D0=6.67%; 历史重复1次; 重复日期=2026-06-01</t>
@@ -15536,24 +12316,12 @@
       <c r="J227" s="5" t="n">
         <v>415.45</v>
       </c>
-      <c r="K227" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L227" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M227" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N227" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O227" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P227" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K227" s="5" t="n"/>
+      <c r="L227" s="5" t="n"/>
+      <c r="M227" s="5" t="n"/>
+      <c r="N227" s="5" t="n"/>
+      <c r="O227" s="5" t="n"/>
+      <c r="P227" s="5" t="n"/>
       <c r="Q227" s="5" t="inlineStr">
         <is>
           <t>D0=361.47; 最新=2026-06-03; 相对D0=14.93%</t>
@@ -15605,24 +12373,6 @@
       <c r="J228" t="n">
         <v>25.2</v>
       </c>
-      <c r="K228" t="n">
-        <v/>
-      </c>
-      <c r="L228" t="n">
-        <v/>
-      </c>
-      <c r="M228" t="n">
-        <v/>
-      </c>
-      <c r="N228" t="n">
-        <v/>
-      </c>
-      <c r="O228" t="n">
-        <v/>
-      </c>
-      <c r="P228" t="n">
-        <v/>
-      </c>
       <c r="Q228" t="inlineStr">
         <is>
           <t>D0=18.88; 最新=2026-06-03; 相对D0=33.47%</t>
@@ -15674,24 +12424,6 @@
       <c r="J229" t="n">
         <v>111.6191</v>
       </c>
-      <c r="K229" t="n">
-        <v/>
-      </c>
-      <c r="L229" t="n">
-        <v/>
-      </c>
-      <c r="M229" t="n">
-        <v/>
-      </c>
-      <c r="N229" t="n">
-        <v/>
-      </c>
-      <c r="O229" t="n">
-        <v/>
-      </c>
-      <c r="P229" t="n">
-        <v/>
-      </c>
       <c r="Q229" t="inlineStr">
         <is>
           <t>D0=114.68; 最新=2026-06-03; 相对D0=-2.67%</t>
@@ -15743,24 +12475,12 @@
       <c r="J230" s="5" t="n">
         <v>133.12</v>
       </c>
-      <c r="K230" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L230" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M230" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N230" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O230" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P230" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K230" s="5" t="n"/>
+      <c r="L230" s="5" t="n"/>
+      <c r="M230" s="5" t="n"/>
+      <c r="N230" s="5" t="n"/>
+      <c r="O230" s="5" t="n"/>
+      <c r="P230" s="5" t="n"/>
       <c r="Q230" s="5" t="inlineStr">
         <is>
           <t>D0=134.08; 最新=2026-06-03; 相对D0=-0.72%</t>
@@ -15812,24 +12532,12 @@
       <c r="J231" s="5" t="n">
         <v>266</v>
       </c>
-      <c r="K231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O231" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P231" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K231" s="5" t="n"/>
+      <c r="L231" s="5" t="n"/>
+      <c r="M231" s="5" t="n"/>
+      <c r="N231" s="5" t="n"/>
+      <c r="O231" s="5" t="n"/>
+      <c r="P231" s="5" t="n"/>
       <c r="Q231" s="5" t="inlineStr">
         <is>
           <t>D0=255.23; 最新=2026-06-03; 相对D0=4.22%</t>
@@ -15881,24 +12589,6 @@
       <c r="J232" t="n">
         <v>107.68</v>
       </c>
-      <c r="K232" t="n">
-        <v/>
-      </c>
-      <c r="L232" t="n">
-        <v/>
-      </c>
-      <c r="M232" t="n">
-        <v/>
-      </c>
-      <c r="N232" t="n">
-        <v/>
-      </c>
-      <c r="O232" t="n">
-        <v/>
-      </c>
-      <c r="P232" t="n">
-        <v/>
-      </c>
       <c r="Q232" t="inlineStr">
         <is>
           <t>D0=105.65; 最新=2026-06-03; 相对D0=1.92%</t>
@@ -15950,24 +12640,12 @@
       <c r="J233" s="5" t="n">
         <v>183.105</v>
       </c>
-      <c r="K233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O233" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P233" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K233" s="5" t="n"/>
+      <c r="L233" s="5" t="n"/>
+      <c r="M233" s="5" t="n"/>
+      <c r="N233" s="5" t="n"/>
+      <c r="O233" s="5" t="n"/>
+      <c r="P233" s="5" t="n"/>
       <c r="Q233" s="5" t="inlineStr">
         <is>
           <t>D0=163.09; 最新=2026-06-03; 相对D0=12.27%</t>
@@ -16019,24 +12697,6 @@
       <c r="J234" t="n">
         <v>66.37</v>
       </c>
-      <c r="K234" t="n">
-        <v/>
-      </c>
-      <c r="L234" t="n">
-        <v/>
-      </c>
-      <c r="M234" t="n">
-        <v/>
-      </c>
-      <c r="N234" t="n">
-        <v/>
-      </c>
-      <c r="O234" t="n">
-        <v/>
-      </c>
-      <c r="P234" t="n">
-        <v/>
-      </c>
       <c r="Q234" t="inlineStr">
         <is>
           <t>D0=64.61; 最新=2026-06-03; 相对D0=2.72%</t>
@@ -16088,24 +12748,12 @@
       <c r="J235" s="5" t="n">
         <v>140.92</v>
       </c>
-      <c r="K235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O235" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P235" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K235" s="5" t="n"/>
+      <c r="L235" s="5" t="n"/>
+      <c r="M235" s="5" t="n"/>
+      <c r="N235" s="5" t="n"/>
+      <c r="O235" s="5" t="n"/>
+      <c r="P235" s="5" t="n"/>
       <c r="Q235" s="5" t="inlineStr">
         <is>
           <t>D0=135.73; 最新=2026-06-03; 相对D0=3.82%</t>
@@ -16157,24 +12805,6 @@
       <c r="J236" t="n">
         <v>617.79</v>
       </c>
-      <c r="K236" t="n">
-        <v/>
-      </c>
-      <c r="L236" t="n">
-        <v/>
-      </c>
-      <c r="M236" t="n">
-        <v/>
-      </c>
-      <c r="N236" t="n">
-        <v/>
-      </c>
-      <c r="O236" t="n">
-        <v/>
-      </c>
-      <c r="P236" t="n">
-        <v/>
-      </c>
       <c r="Q236" t="inlineStr">
         <is>
           <t>D0=600.47; 最新=2026-06-03; 相对D0=2.88%</t>
@@ -16226,24 +12856,12 @@
       <c r="J237" s="5" t="n">
         <v>31.326</v>
       </c>
-      <c r="K237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O237" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P237" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K237" s="5" t="n"/>
+      <c r="L237" s="5" t="n"/>
+      <c r="M237" s="5" t="n"/>
+      <c r="N237" s="5" t="n"/>
+      <c r="O237" s="5" t="n"/>
+      <c r="P237" s="5" t="n"/>
       <c r="Q237" s="5" t="inlineStr">
         <is>
           <t>D0=24.86; 最新=2026-06-03; 相对D0=26.01%</t>
@@ -16294,24 +12912,6 @@
       </c>
       <c r="J238" t="n">
         <v>419.8701</v>
-      </c>
-      <c r="K238" t="n">
-        <v/>
-      </c>
-      <c r="L238" t="n">
-        <v/>
-      </c>
-      <c r="M238" t="n">
-        <v/>
-      </c>
-      <c r="N238" t="n">
-        <v/>
-      </c>
-      <c r="O238" t="n">
-        <v/>
-      </c>
-      <c r="P238" t="n">
-        <v/>
       </c>
       <c r="Q238" t="inlineStr">
         <is>
@@ -16409,7 +13009,6 @@
         <v>3</v>
       </c>
     </row>
-    <row r="247"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -16421,7 +13020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:N43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -16692,7 +13291,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>买入跟踪 | 正式买入 | 第一买入点 | 预警买入</t>
+          <t>买入跟踪 | 正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -16977,7 +13576,6 @@
       <c r="M11" s="19" t="n">
         <v>0.022367</v>
       </c>
-      <c r="N11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
@@ -17162,7 +13760,6 @@
       <c r="F15" t="n">
         <v>1921.71</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>1940.04</v>
       </c>
@@ -17181,7 +13778,6 @@
       <c r="M15" s="19" t="n">
         <v>0.097486</v>
       </c>
-      <c r="N15" t="inlineStr"/>
     </row>
     <row r="16"/>
     <row r="17">
@@ -17434,9 +14030,7 @@
           <t>AEHR</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17482,9 +14076,7 @@
           <t>AMKR</t>
         </is>
       </c>
-      <c r="B28" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B28" s="15" t="n"/>
       <c r="C28" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17530,9 +14122,7 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B29" s="15" t="n"/>
       <c r="C29" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -17578,9 +14168,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="15" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -17630,9 +14218,7 @@
           <t>COHR</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="15" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -17678,9 +14264,7 @@
           <t>FLNC</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="15" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -17726,9 +14310,7 @@
           <t>INTC</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="15" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>03 GPU / AI芯片</t>
@@ -17774,9 +14356,7 @@
           <t>NRG</t>
         </is>
       </c>
-      <c r="B34" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="15" t="n"/>
       <c r="C34" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -17822,9 +14402,7 @@
           <t>TSEM</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -17954,7 +14532,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="44"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -17966,7 +14543,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P47"/>
+  <dimension ref="A1:P44"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -18646,7 +15223,6 @@
       <c r="O12" s="22" t="n">
         <v>-0.014321</v>
       </c>
-      <c r="P12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -18675,7 +15251,6 @@
       <c r="F13" t="n">
         <v>290.01</v>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>285</v>
       </c>
@@ -18762,7 +15337,6 @@
       <c r="O14" s="22" t="n">
         <v>-0.000329</v>
       </c>
-      <c r="P14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -18791,7 +15365,6 @@
       <c r="F15" t="n">
         <v>67.38</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>66.94</v>
       </c>
@@ -18849,7 +15422,6 @@
       <c r="F16" t="n">
         <v>1069.4399</v>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>1068.04</v>
       </c>
@@ -18874,7 +15446,6 @@
       <c r="O16" s="19" t="n">
         <v>0.018332</v>
       </c>
-      <c r="P16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -19515,9 +16086,7 @@
           <t>AXTI</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19569,9 +16138,7 @@
           <t>CEG</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -19623,9 +16190,7 @@
           <t>GLW</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -19677,9 +16242,7 @@
           <t>SNPS</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>04 半导体设备 / EDA</t>
@@ -19789,9 +16352,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45"/>
-    <row r="46"/>
-    <row r="47"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -19803,7 +16363,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -20074,7 +16634,7 @@
       </c>
       <c r="E5" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F5" s="10" t="n">
@@ -20134,7 +16694,7 @@
       </c>
       <c r="E6" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F6" s="10" t="n">
@@ -20328,7 +16888,6 @@
       <c r="F9" t="n">
         <v>190.96</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>203.7</v>
       </c>
@@ -20359,7 +16918,6 @@
       <c r="Q9" s="19" t="n">
         <v>0.198916</v>
       </c>
-      <c r="R9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -20388,7 +16946,6 @@
       <c r="F10" t="n">
         <v>90.87</v>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>91.09</v>
       </c>
@@ -20551,7 +17108,6 @@
       <c r="Q12" s="19" t="n">
         <v>0.036644</v>
       </c>
-      <c r="R12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
@@ -20948,9 +17504,7 @@
           <t>SLB</t>
         </is>
       </c>
-      <c r="B26" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B26" s="15" t="n"/>
       <c r="C26" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -21008,9 +17562,7 @@
           <t>ZS</t>
         </is>
       </c>
-      <c r="B27" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B27" s="15" t="n"/>
       <c r="C27" s="5" t="inlineStr">
         <is>
           <t>12 网络安全</t>
@@ -21113,10 +17665,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="33"/>
-    <row r="34"/>
-    <row r="35"/>
-    <row r="36"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -21128,7 +17676,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T56"/>
+  <dimension ref="A1:T54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -21563,7 +18111,7 @@
       </c>
       <c r="E7" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F7" s="10" t="n">
@@ -21705,7 +18253,6 @@
       <c r="F9" t="n">
         <v>105.89</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>104.27</v>
       </c>
@@ -22877,7 +19424,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F26" t="n">
@@ -22924,7 +19471,6 @@
       <c r="S26" s="19" t="n">
         <v>0.03603</v>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -22947,7 +19493,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -23079,7 +19625,7 @@
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>买入跟踪 | 第一买入点</t>
+          <t>买入跟踪 | 第一观察点</t>
         </is>
       </c>
       <c r="F29" s="5" t="n">
@@ -23409,9 +19955,7 @@
           <t>CCI</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>99 未分组</t>
@@ -23475,9 +20019,7 @@
           <t>CVX</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23541,9 +20083,7 @@
           <t>EOG</t>
         </is>
       </c>
-      <c r="B43" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="15" t="n"/>
       <c r="C43" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23607,9 +20147,7 @@
           <t>MDB</t>
         </is>
       </c>
-      <c r="B44" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B44" s="15" t="n"/>
       <c r="C44" s="5" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -23673,9 +20211,7 @@
           <t>OXY</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23739,9 +20275,7 @@
           <t>POET</t>
         </is>
       </c>
-      <c r="B46" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B46" s="15" t="n"/>
       <c r="C46" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -23805,9 +20339,7 @@
           <t>XLE</t>
         </is>
       </c>
-      <c r="B47" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B47" s="15" t="n"/>
       <c r="C47" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -23942,8 +20474,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="55"/>
-    <row r="56"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -23955,7 +20485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q42"/>
+  <dimension ref="A1:Q37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -24116,24 +20646,12 @@
       <c r="J3" s="5" t="n">
         <v>181.49</v>
       </c>
-      <c r="K3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O3" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P3" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K3" s="5" t="n"/>
+      <c r="L3" s="5" t="n"/>
+      <c r="M3" s="5" t="n"/>
+      <c r="N3" s="5" t="n"/>
+      <c r="O3" s="5" t="n"/>
+      <c r="P3" s="5" t="n"/>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>D0=181.49; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24185,24 +20703,12 @@
       <c r="J4" s="5" t="n">
         <v>202.91</v>
       </c>
-      <c r="K4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O4" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P4" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K4" s="5" t="n"/>
+      <c r="L4" s="5" t="n"/>
+      <c r="M4" s="5" t="n"/>
+      <c r="N4" s="5" t="n"/>
+      <c r="O4" s="5" t="n"/>
+      <c r="P4" s="5" t="n"/>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>D0=202.91; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24254,24 +20760,12 @@
       <c r="J5" s="5" t="n">
         <v>167.37</v>
       </c>
-      <c r="K5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O5" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P5" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K5" s="5" t="n"/>
+      <c r="L5" s="5" t="n"/>
+      <c r="M5" s="5" t="n"/>
+      <c r="N5" s="5" t="n"/>
+      <c r="O5" s="5" t="n"/>
+      <c r="P5" s="5" t="n"/>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>D0=167.37; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24323,24 +20817,12 @@
       <c r="J6" s="5" t="n">
         <v>46.53</v>
       </c>
-      <c r="K6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O6" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P6" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K6" s="5" t="n"/>
+      <c r="L6" s="5" t="n"/>
+      <c r="M6" s="5" t="n"/>
+      <c r="N6" s="5" t="n"/>
+      <c r="O6" s="5" t="n"/>
+      <c r="P6" s="5" t="n"/>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>D0=46.53; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24392,24 +20874,6 @@
       <c r="J7" t="n">
         <v>16.12</v>
       </c>
-      <c r="K7" t="n">
-        <v/>
-      </c>
-      <c r="L7" t="n">
-        <v/>
-      </c>
-      <c r="M7" t="n">
-        <v/>
-      </c>
-      <c r="N7" t="n">
-        <v/>
-      </c>
-      <c r="O7" t="n">
-        <v/>
-      </c>
-      <c r="P7" t="n">
-        <v/>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
           <t>D0=16.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24461,24 +20925,12 @@
       <c r="J8" s="5" t="n">
         <v>180.07</v>
       </c>
-      <c r="K8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O8" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P8" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K8" s="5" t="n"/>
+      <c r="L8" s="5" t="n"/>
+      <c r="M8" s="5" t="n"/>
+      <c r="N8" s="5" t="n"/>
+      <c r="O8" s="5" t="n"/>
+      <c r="P8" s="5" t="n"/>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>D0=180.07; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24530,24 +20982,12 @@
       <c r="J9" s="5" t="n">
         <v>48.12</v>
       </c>
-      <c r="K9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O9" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P9" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
+      <c r="M9" s="5" t="n"/>
+      <c r="N9" s="5" t="n"/>
+      <c r="O9" s="5" t="n"/>
+      <c r="P9" s="5" t="n"/>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>D0=48.12; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24599,24 +21039,6 @@
       <c r="J10" t="n">
         <v>141.22</v>
       </c>
-      <c r="K10" t="n">
-        <v/>
-      </c>
-      <c r="L10" t="n">
-        <v/>
-      </c>
-      <c r="M10" t="n">
-        <v/>
-      </c>
-      <c r="N10" t="n">
-        <v/>
-      </c>
-      <c r="O10" t="n">
-        <v/>
-      </c>
-      <c r="P10" t="n">
-        <v/>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
           <t>D0=141.22; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24668,24 +21090,12 @@
       <c r="J11" s="5" t="n">
         <v>391.35</v>
       </c>
-      <c r="K11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O11" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P11" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K11" s="5" t="n"/>
+      <c r="L11" s="5" t="n"/>
+      <c r="M11" s="5" t="n"/>
+      <c r="N11" s="5" t="n"/>
+      <c r="O11" s="5" t="n"/>
+      <c r="P11" s="5" t="n"/>
       <c r="Q11" s="5" t="inlineStr">
         <is>
           <t>D0=391.35; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24737,24 +21147,12 @@
       <c r="J12" s="5" t="n">
         <v>1038.74</v>
       </c>
-      <c r="K12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O12" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P12" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K12" s="5" t="n"/>
+      <c r="L12" s="5" t="n"/>
+      <c r="M12" s="5" t="n"/>
+      <c r="N12" s="5" t="n"/>
+      <c r="O12" s="5" t="n"/>
+      <c r="P12" s="5" t="n"/>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>D0=1038.74; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24806,24 +21204,12 @@
       <c r="J13" s="5" t="n">
         <v>179.36</v>
       </c>
-      <c r="K13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O13" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P13" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K13" s="5" t="n"/>
+      <c r="L13" s="5" t="n"/>
+      <c r="M13" s="5" t="n"/>
+      <c r="N13" s="5" t="n"/>
+      <c r="O13" s="5" t="n"/>
+      <c r="P13" s="5" t="n"/>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>D0=179.36; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24875,24 +21261,12 @@
       <c r="J14" s="5" t="n">
         <v>326.13</v>
       </c>
-      <c r="K14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O14" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P14" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K14" s="5" t="n"/>
+      <c r="L14" s="5" t="n"/>
+      <c r="M14" s="5" t="n"/>
+      <c r="N14" s="5" t="n"/>
+      <c r="O14" s="5" t="n"/>
+      <c r="P14" s="5" t="n"/>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>D0=326.13; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -24944,24 +21318,6 @@
       <c r="J15" t="n">
         <v>22.51</v>
       </c>
-      <c r="K15" t="n">
-        <v/>
-      </c>
-      <c r="L15" t="n">
-        <v/>
-      </c>
-      <c r="M15" t="n">
-        <v/>
-      </c>
-      <c r="N15" t="n">
-        <v/>
-      </c>
-      <c r="O15" t="n">
-        <v/>
-      </c>
-      <c r="P15" t="n">
-        <v/>
-      </c>
       <c r="Q15" t="inlineStr">
         <is>
           <t>D0=22.51; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25013,24 +21369,6 @@
       <c r="J16" t="n">
         <v>232</v>
       </c>
-      <c r="K16" t="n">
-        <v/>
-      </c>
-      <c r="L16" t="n">
-        <v/>
-      </c>
-      <c r="M16" t="n">
-        <v/>
-      </c>
-      <c r="N16" t="n">
-        <v/>
-      </c>
-      <c r="O16" t="n">
-        <v/>
-      </c>
-      <c r="P16" t="n">
-        <v/>
-      </c>
       <c r="Q16" t="inlineStr">
         <is>
           <t>D0=232.00; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25082,24 +21420,6 @@
       <c r="J17" t="n">
         <v>130.5</v>
       </c>
-      <c r="K17" t="n">
-        <v/>
-      </c>
-      <c r="L17" t="n">
-        <v/>
-      </c>
-      <c r="M17" t="n">
-        <v/>
-      </c>
-      <c r="N17" t="n">
-        <v/>
-      </c>
-      <c r="O17" t="n">
-        <v/>
-      </c>
-      <c r="P17" t="n">
-        <v/>
-      </c>
       <c r="Q17" t="inlineStr">
         <is>
           <t>D0=130.50; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25151,24 +21471,12 @@
       <c r="J18" s="5" t="n">
         <v>262.25</v>
       </c>
-      <c r="K18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O18" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P18" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K18" s="5" t="n"/>
+      <c r="L18" s="5" t="n"/>
+      <c r="M18" s="5" t="n"/>
+      <c r="N18" s="5" t="n"/>
+      <c r="O18" s="5" t="n"/>
+      <c r="P18" s="5" t="n"/>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>D0=262.25; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25220,24 +21528,12 @@
       <c r="J19" s="5" t="n">
         <v>85.42</v>
       </c>
-      <c r="K19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O19" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P19" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K19" s="5" t="n"/>
+      <c r="L19" s="5" t="n"/>
+      <c r="M19" s="5" t="n"/>
+      <c r="N19" s="5" t="n"/>
+      <c r="O19" s="5" t="n"/>
+      <c r="P19" s="5" t="n"/>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>D0=85.42; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25289,24 +21585,6 @@
       <c r="J20" t="n">
         <v>426.01</v>
       </c>
-      <c r="K20" t="n">
-        <v/>
-      </c>
-      <c r="L20" t="n">
-        <v/>
-      </c>
-      <c r="M20" t="n">
-        <v/>
-      </c>
-      <c r="N20" t="n">
-        <v/>
-      </c>
-      <c r="O20" t="n">
-        <v/>
-      </c>
-      <c r="P20" t="n">
-        <v/>
-      </c>
       <c r="Q20" t="inlineStr">
         <is>
           <t>D0=426.01; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25358,24 +21636,12 @@
       <c r="J21" s="5" t="n">
         <v>13.02</v>
       </c>
-      <c r="K21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O21" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P21" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K21" s="5" t="n"/>
+      <c r="L21" s="5" t="n"/>
+      <c r="M21" s="5" t="n"/>
+      <c r="N21" s="5" t="n"/>
+      <c r="O21" s="5" t="n"/>
+      <c r="P21" s="5" t="n"/>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>D0=13.02; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25612,24 +21878,12 @@
       <c r="J33" s="5" t="n">
         <v>41.47</v>
       </c>
-      <c r="K33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="L33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="M33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="O33" s="5" t="n">
-        <v/>
-      </c>
-      <c r="P33" s="5" t="n">
-        <v/>
-      </c>
+      <c r="K33" s="5" t="n"/>
+      <c r="L33" s="5" t="n"/>
+      <c r="M33" s="5" t="n"/>
+      <c r="N33" s="5" t="n"/>
+      <c r="O33" s="5" t="n"/>
+      <c r="P33" s="5" t="n"/>
       <c r="Q33" s="5" t="inlineStr">
         <is>
           <t>D0=41.47; 最新=2026-05-22; 相对D0=0.00%</t>
@@ -25674,11 +21928,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38"/>
-    <row r="39"/>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -25690,7 +21939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V54"/>
+  <dimension ref="A1:V49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -25863,7 +22112,6 @@
       <c r="F3" t="n">
         <v>22.51</v>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>22.62</v>
       </c>
@@ -26319,7 +22567,6 @@
       <c r="F9" t="n">
         <v>181.49</v>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>177.62</v>
       </c>
@@ -26771,7 +23018,6 @@
       <c r="F15" t="n">
         <v>16.12</v>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>15.47</v>
       </c>
@@ -26923,7 +23169,6 @@
       <c r="F17" t="n">
         <v>610.26</v>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>612.34</v>
       </c>
@@ -27299,7 +23544,6 @@
       <c r="F22" t="n">
         <v>141.22</v>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>136.2</v>
       </c>
@@ -27375,7 +23619,6 @@
       <c r="F23" t="n">
         <v>58.81</v>
       </c>
-      <c r="G23" t="inlineStr"/>
       <c r="H23" t="n">
         <v>57.46</v>
       </c>
@@ -27451,7 +23694,6 @@
       <c r="F24" t="n">
         <v>81.76000000000001</v>
       </c>
-      <c r="G24" t="inlineStr"/>
       <c r="H24" t="n">
         <v>84.64</v>
       </c>
@@ -27521,7 +23763,7 @@
       </c>
       <c r="E25" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F25" s="5" t="n">
@@ -27603,7 +23845,6 @@
       <c r="F26" t="n">
         <v>426.01</v>
       </c>
-      <c r="G26" t="inlineStr"/>
       <c r="H26" t="n">
         <v>433.59</v>
       </c>
@@ -27646,7 +23887,6 @@
       <c r="U26" s="22" t="n">
         <v>-0.014366</v>
       </c>
-      <c r="V26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
@@ -27669,7 +23909,7 @@
       </c>
       <c r="E27" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F27" s="5" t="n">
@@ -27973,7 +24213,7 @@
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F31" s="5" t="n">
@@ -28049,7 +24289,7 @@
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>第一买入点</t>
+          <t>第一观察点</t>
         </is>
       </c>
       <c r="F32" s="5" t="n">
@@ -28463,9 +24703,7 @@
           <t>HAL</t>
         </is>
       </c>
-      <c r="B45" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B45" s="15" t="n"/>
       <c r="C45" s="5" t="inlineStr">
         <is>
           <t>14 能源</t>
@@ -28567,11 +24805,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50"/>
-    <row r="51"/>
-    <row r="52"/>
-    <row r="53"/>
-    <row r="54"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -28789,7 +25022,6 @@
       <c r="V2" t="n">
         <v>205.7700042724609</v>
       </c>
-      <c r="W2" t="inlineStr"/>
       <c r="X2" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.80; 4H分金=48.04</t>
@@ -28877,7 +25109,6 @@
       <c r="V3" t="n">
         <v>275.4400024414062</v>
       </c>
-      <c r="W3" t="inlineStr"/>
       <c r="X3" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.03; 4H分金=48.82</t>
@@ -28959,8 +25190,6 @@
       <c r="T4" t="b">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
         <v>87</v>
       </c>
@@ -29051,7 +25280,6 @@
       <c r="V5" t="n">
         <v>50.72499847412109</v>
       </c>
-      <c r="W5" t="inlineStr"/>
       <c r="X5" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-28; 1出价格=50.72; Gann0=35.68; 段涨幅=42.17%</t>
@@ -29139,7 +25367,6 @@
       <c r="V6" t="n">
         <v>50.72499847412109</v>
       </c>
-      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.33; 4H分金=37.91</t>
@@ -29221,8 +25448,6 @@
       <c r="T7" t="b">
         <v>0</v>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
       <c r="W7" t="n">
         <v>87</v>
       </c>
@@ -29403,7 +25628,6 @@
       <c r="V9" t="n">
         <v>16.90999984741211</v>
       </c>
-      <c r="W9" t="inlineStr"/>
       <c r="X9" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=16.91; Gann0=15.03; 段涨幅=12.51%</t>
@@ -29491,7 +25715,6 @@
       <c r="V10" t="n">
         <v>16.90999984741211</v>
       </c>
-      <c r="W10" t="inlineStr"/>
       <c r="X10" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.69; 4H分金=43.82</t>
@@ -29579,7 +25802,6 @@
       <c r="V11" t="n">
         <v>245.9499969482422</v>
       </c>
-      <c r="W11" t="inlineStr"/>
       <c r="X11" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=245.95; Gann0=148.95; 段涨幅=65.13%</t>
@@ -29667,7 +25889,6 @@
       <c r="V12" t="n">
         <v>211.3399963378906</v>
       </c>
-      <c r="W12" t="inlineStr"/>
       <c r="X12" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=54.57; 4H分金=48.32</t>
@@ -29755,7 +25976,6 @@
       <c r="V13" t="n">
         <v>132.1499938964844</v>
       </c>
-      <c r="W13" t="inlineStr"/>
       <c r="X13" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=132.15; Gann0=94.82; 段涨幅=39.37%</t>
@@ -29843,7 +26063,6 @@
       <c r="V14" t="n">
         <v>132.1499938964844</v>
       </c>
-      <c r="W14" t="inlineStr"/>
       <c r="X14" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.39; 4H分金=44.54</t>
@@ -29931,7 +26150,6 @@
       <c r="V15" t="n">
         <v>278.7049865722656</v>
       </c>
-      <c r="W15" t="inlineStr"/>
       <c r="X15" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.03; 4H分金=46.88</t>
@@ -30013,8 +26231,6 @@
       <c r="T16" t="b">
         <v>0</v>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr"/>
       <c r="W16" t="n">
         <v>90</v>
       </c>
@@ -30105,7 +26321,6 @@
       <c r="V17" t="n">
         <v>9.689999580383301</v>
       </c>
-      <c r="W17" t="inlineStr"/>
       <c r="X17" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=9.69; Gann0=6.73; 段涨幅=43.98%</t>
@@ -30193,7 +26408,6 @@
       <c r="V18" t="n">
         <v>9.689999580383301</v>
       </c>
-      <c r="W18" t="inlineStr"/>
       <c r="X18" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=50.03; 4H分金=39.35</t>
@@ -30371,7 +26585,6 @@
       <c r="V20" t="n">
         <v>94.40000152587891</v>
       </c>
-      <c r="W20" t="inlineStr"/>
       <c r="X20" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=52.60; 4H分金=41.18</t>
@@ -30459,7 +26672,6 @@
       <c r="V21" t="n">
         <v>108.0599975585938</v>
       </c>
-      <c r="W21" t="inlineStr"/>
       <c r="X21" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=57.48; 4H分金=46.27</t>
@@ -30727,7 +26939,6 @@
       <c r="V24" t="n">
         <v>204.8000030517578</v>
       </c>
-      <c r="W24" t="inlineStr"/>
       <c r="X24" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=46.09; 4H分金=40.44</t>
@@ -30995,7 +27206,6 @@
       <c r="V27" t="n">
         <v>1049.530029296875</v>
       </c>
-      <c r="W27" t="inlineStr"/>
       <c r="X27" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=51.09; 4H分金=50.29</t>
@@ -31533,7 +27743,6 @@
       <c r="V33" t="n">
         <v>466.3200073242188</v>
       </c>
-      <c r="W33" t="inlineStr"/>
       <c r="X33" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=466.32; Gann0=409.58; 段涨幅=13.85%</t>
@@ -31621,7 +27830,6 @@
       <c r="V34" t="n">
         <v>466.3200073242188</v>
       </c>
-      <c r="W34" t="inlineStr"/>
       <c r="X34" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.96; 4H分金=36.15</t>
@@ -31709,7 +27917,6 @@
       <c r="V35" t="n">
         <v>31.59000015258789</v>
       </c>
-      <c r="W35" t="inlineStr"/>
       <c r="X35" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=31.59; Gann0=21.72; 段涨幅=45.46%</t>
@@ -31797,7 +28004,6 @@
       <c r="V36" t="n">
         <v>31.59000015258789</v>
       </c>
-      <c r="W36" t="inlineStr"/>
       <c r="X36" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=44.10; 4H分金=30.78</t>
@@ -31885,7 +28091,6 @@
       <c r="V37" t="n">
         <v>139.1999969482422</v>
       </c>
-      <c r="W37" t="inlineStr"/>
       <c r="X37" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=59.42; 4H分金=48.69</t>
@@ -31967,8 +28172,6 @@
       <c r="T38" t="b">
         <v>0</v>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr"/>
       <c r="W38" t="n">
         <v>95</v>
       </c>
@@ -32059,7 +28262,6 @@
       <c r="V39" t="n">
         <v>232.2799987792969</v>
       </c>
-      <c r="W39" t="inlineStr"/>
       <c r="X39" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=47.18; 4H分金=40.87</t>
@@ -32237,7 +28439,6 @@
       <c r="V41" t="n">
         <v>163.1300048828125</v>
       </c>
-      <c r="W41" t="inlineStr"/>
       <c r="X41" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.32; 4H分金=49.92</t>
@@ -32325,7 +28526,6 @@
       <c r="V42" t="n">
         <v>73.86000061035156</v>
       </c>
-      <c r="W42" t="inlineStr"/>
       <c r="X42" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=73.86; Gann0=53.96; 段涨幅=36.89%</t>
@@ -32413,7 +28613,6 @@
       <c r="V43" t="n">
         <v>302.9500122070312</v>
       </c>
-      <c r="W43" t="inlineStr"/>
       <c r="X43" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=61.66; 4H分金=49.52</t>
@@ -32501,7 +28700,6 @@
       <c r="V44" t="n">
         <v>163.6999969482422</v>
       </c>
-      <c r="W44" t="inlineStr"/>
       <c r="X44" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=163.70; Gann0=131.63; 段涨幅=24.36%</t>
@@ -32589,7 +28787,6 @@
       <c r="V45" t="n">
         <v>163.6999969482422</v>
       </c>
-      <c r="W45" t="inlineStr"/>
       <c r="X45" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.73; 4H分金=37.01</t>
@@ -32677,7 +28874,6 @@
       <c r="V46" t="n">
         <v>112.2099990844727</v>
       </c>
-      <c r="W46" t="inlineStr"/>
       <c r="X46" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.55; 4H分金=49.93</t>
@@ -32765,7 +28961,6 @@
       <c r="V47" t="n">
         <v>16.76000022888184</v>
       </c>
-      <c r="W47" t="inlineStr"/>
       <c r="X47" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-29; 1出价格=16.76; Gann0=12.71; 段涨幅=31.86%</t>
@@ -32853,7 +29048,6 @@
       <c r="V48" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="W48" t="inlineStr"/>
       <c r="X48" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-02; 1出价格=14.30; Gann0=9.66; 段涨幅=47.96%</t>
@@ -32941,7 +29135,6 @@
       <c r="V49" t="n">
         <v>14.30000019073486</v>
       </c>
-      <c r="W49" t="inlineStr"/>
       <c r="X49" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=49.00; 4H分金=40.47</t>
@@ -33023,8 +29216,6 @@
       <c r="T50" t="b">
         <v>0</v>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr"/>
       <c r="W50" t="n">
         <v>85</v>
       </c>
@@ -33115,7 +29306,6 @@
       <c r="V51" t="n">
         <v>18.79500007629395</v>
       </c>
-      <c r="W51" t="inlineStr"/>
       <c r="X51" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-06-01; 1出价格=18.80; Gann0=14.92; 段涨幅=25.97%</t>
@@ -33203,7 +29393,6 @@
       <c r="V52" t="n">
         <v>18.79500007629395</v>
       </c>
-      <c r="W52" t="inlineStr"/>
       <c r="X52" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=48.71; 4H分金=36.55</t>
@@ -33291,7 +29480,6 @@
       <c r="V53" t="n">
         <v>75.59999847412109</v>
       </c>
-      <c r="W53" t="inlineStr"/>
       <c r="X53" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=55.95; 4H分金=42.23</t>
@@ -33379,7 +29567,6 @@
       <c r="V54" t="n">
         <v>119.379997253418</v>
       </c>
-      <c r="W54" t="inlineStr"/>
       <c r="X54" t="inlineStr">
         <is>
           <t>4H 1出; 4H_RSI=56.76; 4H分金=46.77</t>
@@ -33737,7 +29924,6 @@
       <c r="V58" t="n">
         <v>167.3999938964844</v>
       </c>
-      <c r="W58" t="inlineStr"/>
       <c r="X58" t="inlineStr">
         <is>
           <t>日线1出确认; 1出日期=2026-05-26; 1出价格=167.40; Gann0=132.66; 段涨幅=26.19%</t>
@@ -33950,7 +30136,6 @@
       <c r="D3" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" s="8" t="n">
         <v>46175</v>
       </c>
@@ -34056,7 +30241,6 @@
       <c r="D5" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E5" t="inlineStr"/>
       <c r="F5" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34216,7 +30400,6 @@
       <c r="D8" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E8" t="inlineStr"/>
       <c r="F8" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34268,7 +30451,6 @@
       <c r="D9" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E9" t="inlineStr"/>
       <c r="F9" s="8" t="n">
         <v>46168</v>
       </c>
@@ -34320,7 +30502,6 @@
       <c r="D10" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34372,7 +30553,6 @@
       <c r="D11" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" s="8" t="n">
         <v>46175</v>
       </c>
@@ -34478,7 +30658,6 @@
       <c r="D13" s="8" t="n">
         <v>46174</v>
       </c>
-      <c r="E13" t="inlineStr"/>
       <c r="F13" s="8" t="n">
         <v>46174</v>
       </c>
@@ -34530,7 +30709,6 @@
       <c r="D14" s="8" t="n">
         <v>46168</v>
       </c>
-      <c r="E14" t="inlineStr"/>
       <c r="F14" s="8" t="n">
         <v>46168</v>
       </c>
@@ -34636,7 +30814,6 @@
       <c r="D16" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E16" t="inlineStr"/>
       <c r="F16" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34688,7 +30865,6 @@
       <c r="D17" s="8" t="n">
         <v>46175</v>
       </c>
-      <c r="E17" t="inlineStr"/>
       <c r="F17" s="8" t="n">
         <v>46175</v>
       </c>
@@ -34737,7 +30913,6 @@
           <t>19 COWOS</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
       <c r="E18" s="8" t="n">
         <v>46164</v>
       </c>
@@ -34846,7 +31021,6 @@
       <c r="D20" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E20" t="inlineStr"/>
       <c r="F20" s="8" t="n">
         <v>46164</v>
       </c>
@@ -35006,7 +31180,6 @@
       <c r="D23" s="8" t="n">
         <v>46164</v>
       </c>
-      <c r="E23" t="inlineStr"/>
       <c r="F23" s="8" t="n">
         <v>46164</v>
       </c>
@@ -35839,7 +32012,6 @@
       <c r="I13" t="n">
         <v>2</v>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" s="8" t="n">
         <v>46175</v>
       </c>
@@ -36521,7 +32693,6 @@
       <c r="I25" t="n">
         <v>4</v>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" s="8" t="n">
         <v>46171</v>
       </c>
@@ -36633,7 +32804,6 @@
       <c r="I27" t="n">
         <v>6</v>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" s="8" t="n">
         <v>46169</v>
       </c>
@@ -36665,7 +32835,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H52"/>
+  <dimension ref="A1:H51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -37207,7 +33377,6 @@
           <t>2026-06-02 (83)</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -37453,9 +33622,7 @@
           <t>APLD</t>
         </is>
       </c>
-      <c r="B30" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B30" s="15" t="n"/>
       <c r="C30" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -37483,9 +33650,7 @@
           <t>CPNG</t>
         </is>
       </c>
-      <c r="B31" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B31" s="15" t="n"/>
       <c r="C31" s="5" t="inlineStr">
         <is>
           <t>23 杂项</t>
@@ -37513,9 +33678,7 @@
           <t>CRDO</t>
         </is>
       </c>
-      <c r="B32" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B32" s="15" t="n"/>
       <c r="C32" s="5" t="inlineStr">
         <is>
           <t>05 AI网络 / 光模块</t>
@@ -37543,9 +33706,7 @@
           <t>CRWV</t>
         </is>
       </c>
-      <c r="B33" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B33" s="15" t="n"/>
       <c r="C33" s="5" t="inlineStr">
         <is>
           <t>21 数据中心</t>
@@ -37573,9 +33734,7 @@
           <t>EOSE</t>
         </is>
       </c>
-      <c r="B34" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B34" s="16" t="n"/>
       <c r="C34" t="inlineStr">
         <is>
           <t>09 储能</t>
@@ -37594,8 +33753,6 @@
       <c r="F34" t="n">
         <v>8.385</v>
       </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
@@ -37603,9 +33760,7 @@
           <t>HOOD</t>
         </is>
       </c>
-      <c r="B35" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B35" s="15" t="n"/>
       <c r="C35" s="5" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -37633,9 +33788,7 @@
           <t>MSFT</t>
         </is>
       </c>
-      <c r="B36" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="16" t="n"/>
       <c r="C36" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -37654,8 +33807,6 @@
       <c r="F36" t="n">
         <v>425.555</v>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -37663,9 +33814,7 @@
           <t>NNE</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -37693,9 +33842,7 @@
           <t>OKLO</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -37723,9 +33870,7 @@
           <t>PLTR</t>
         </is>
       </c>
-      <c r="B39" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="16" t="n"/>
       <c r="C39" t="inlineStr">
         <is>
           <t>11 AI软件 / SAAS</t>
@@ -37744,8 +33889,6 @@
       <c r="F39" t="n">
         <v>142.81</v>
       </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -37753,9 +33896,7 @@
           <t>RUN</t>
         </is>
       </c>
-      <c r="B40" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="16" t="n"/>
       <c r="C40" t="inlineStr">
         <is>
           <t>10 太阳能</t>
@@ -37774,8 +33915,6 @@
       <c r="F40" t="n">
         <v>14.7064</v>
       </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
@@ -37783,9 +33922,7 @@
           <t>SMR</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>08 核能</t>
@@ -37813,9 +33950,7 @@
           <t>SOFI</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>16 金融股</t>
@@ -37843,9 +33978,7 @@
           <t>VST</t>
         </is>
       </c>
-      <c r="B43" s="16" t="n">
-        <v/>
-      </c>
+      <c r="B43" s="16" t="n"/>
       <c r="C43" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -37864,8 +33997,6 @@
       <c r="F43" t="n">
         <v>153.41</v>
       </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
     </row>
     <row r="44"/>
     <row r="45">
@@ -37957,7 +34088,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -38201,7 +34331,6 @@
       <c r="I6" s="19" t="n">
         <v>0.005794</v>
       </c>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
@@ -38304,7 +34433,7 @@
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F9" s="10" t="n">
@@ -38344,7 +34473,7 @@
       </c>
       <c r="E10" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F10" s="10" t="n">
@@ -38384,7 +34513,7 @@
       </c>
       <c r="E11" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点</t>
+          <t>正式买入 | 第一观察点</t>
         </is>
       </c>
       <c r="F11" s="10" t="n">
@@ -39213,7 +35342,6 @@
       <c r="I32" s="19" t="n">
         <v>0.003009</v>
       </c>
-      <c r="J32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="5" t="inlineStr">
@@ -39329,7 +35457,6 @@
       <c r="I35" s="19" t="n">
         <v>0.006328</v>
       </c>
-      <c r="J35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -39369,7 +35496,6 @@
       <c r="I36" s="19" t="n">
         <v>0.002403</v>
       </c>
-      <c r="J36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
@@ -39474,14 +35600,12 @@
       <c r="F39" t="n">
         <v>315.2</v>
       </c>
-      <c r="G39" t="inlineStr"/>
       <c r="H39" t="n">
         <v>309.355</v>
       </c>
       <c r="I39" s="22" t="n">
         <v>-0.018544</v>
       </c>
-      <c r="J39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -39510,14 +35634,12 @@
       <c r="F40" t="n">
         <v>72.33</v>
       </c>
-      <c r="G40" t="inlineStr"/>
       <c r="H40" t="n">
         <v>67.94</v>
       </c>
       <c r="I40" s="22" t="n">
         <v>-0.060694</v>
       </c>
-      <c r="J40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -39546,14 +35668,12 @@
       <c r="F41" t="n">
         <v>11.72</v>
       </c>
-      <c r="G41" t="inlineStr"/>
       <c r="H41" t="n">
         <v>11.1214</v>
       </c>
       <c r="I41" s="22" t="n">
         <v>-0.051075</v>
       </c>
-      <c r="J41" t="inlineStr"/>
     </row>
     <row r="42"/>
     <row r="43">
@@ -39783,7 +35903,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L51"/>
+  <dimension ref="A1:L50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
@@ -39890,7 +36010,7 @@
       </c>
       <c r="E3" s="12" t="inlineStr">
         <is>
-          <t>正式买入 | 第一买入点 | 预警买入</t>
+          <t>正式买入 | 第一观察点 | 预警买入</t>
         </is>
       </c>
       <c r="F3" s="10" t="n">
@@ -40114,7 +36234,6 @@
       <c r="F8" t="n">
         <v>69.56999999999999</v>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>68.5</v>
       </c>
@@ -40248,7 +36367,6 @@
       <c r="F11" t="n">
         <v>14.7</v>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>14.68</v>
       </c>
@@ -40261,7 +36379,6 @@
       <c r="K11" s="19" t="n">
         <v>0.00068</v>
       </c>
-      <c r="L11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
@@ -40382,7 +36499,6 @@
       <c r="F14" t="n">
         <v>15.58</v>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>15.25</v>
       </c>
@@ -40395,7 +36511,6 @@
       <c r="K14" s="22" t="n">
         <v>-0.056483</v>
       </c>
-      <c r="L14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="10" t="inlineStr">
@@ -40533,7 +36648,6 @@
       <c r="K17" s="19" t="n">
         <v>0.032159</v>
       </c>
-      <c r="L17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
@@ -41090,9 +37204,7 @@
           <t>ASTS</t>
         </is>
       </c>
-      <c r="B36" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B36" s="15" t="n"/>
       <c r="C36" s="5" t="inlineStr">
         <is>
           <t>17 高弹性交易池</t>
@@ -41132,9 +37244,7 @@
           <t>CAMT</t>
         </is>
       </c>
-      <c r="B37" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B37" s="15" t="n"/>
       <c r="C37" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -41178,9 +37288,7 @@
           <t>D</t>
         </is>
       </c>
-      <c r="B38" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B38" s="15" t="n"/>
       <c r="C38" s="5" t="inlineStr">
         <is>
           <t>15 公用事业</t>
@@ -41220,9 +37328,7 @@
           <t>ENTG</t>
         </is>
       </c>
-      <c r="B39" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B39" s="15" t="n"/>
       <c r="C39" s="5" t="inlineStr">
         <is>
           <t>19 COWOS</t>
@@ -41262,9 +37368,7 @@
           <t>META</t>
         </is>
       </c>
-      <c r="B40" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B40" s="15" t="n"/>
       <c r="C40" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -41304,9 +37408,7 @@
           <t>NVTS</t>
         </is>
       </c>
-      <c r="B41" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B41" s="15" t="n"/>
       <c r="C41" s="5" t="inlineStr">
         <is>
           <t>07 数据中心电力</t>
@@ -41346,9 +37448,7 @@
           <t>TSLA</t>
         </is>
       </c>
-      <c r="B42" s="15" t="n">
-        <v/>
-      </c>
+      <c r="B42" s="15" t="n"/>
       <c r="C42" s="5" t="inlineStr">
         <is>
           <t>02 超巨</t>
@@ -41472,7 +37572,6 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51"/>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
